--- a/processed-data/21_Xenium/02_xenium_compile_custom/ERC_Xenium_ALL_probes_summary.xlsx
+++ b/processed-data/21_Xenium/02_xenium_compile_custom/ERC_Xenium_ALL_probes_summary.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G375"/>
+  <dimension ref="A1:G370"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2347,28 +2347,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CFHR5</t>
+          <t>CHODL</t>
         </is>
       </c>
       <c r="B65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65">
         <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>WM.uf_Sp09D07-WM_Sp09D06</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SpD pw gene t=8.23</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G65" t="b">
@@ -2378,28 +2378,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CHODL</t>
+          <t>CHRM3</t>
         </is>
       </c>
       <c r="B66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>mediation gene: mediator Astro.3</t>
         </is>
       </c>
       <c r="G66" t="b">
@@ -2409,7 +2409,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CHRM3</t>
+          <t>CHST11</t>
         </is>
       </c>
       <c r="B67" t="b">
@@ -2420,17 +2420,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.3</t>
+          <t>DEG carrier top: Oligo.3 up logFC=2.82</t>
         </is>
       </c>
       <c r="G67" t="b">
@@ -2440,28 +2440,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CHST11</t>
+          <t>CLDN11</t>
         </is>
       </c>
       <c r="B68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 up</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G68" t="b">
@@ -2471,28 +2471,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CLDN11</t>
+          <t>CNDP1</t>
         </is>
       </c>
       <c r="B69" t="b">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Astro.3, Inhib.Vip, Oligo, Oligo.3</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Base probe - Oligo, DEG carrier included: Astro.3 down, DEG carrier included: Oligo.3 down, DEG carrier included: Inhib.Vip down</t>
         </is>
       </c>
       <c r="G69" t="b">
@@ -2502,28 +2502,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CNDP1</t>
+          <t>CNTN2</t>
         </is>
       </c>
       <c r="B70" t="b">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Astro.3, Inhib.Vip, Oligo, Oligo.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, DEG carrier included: Astro.3 down, DEG carrier included: Oligo.3 down, DEG carrier included: Inhib.Vip down</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G70" t="b">
@@ -2533,28 +2533,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CNTN2</t>
+          <t>CNTNAP2</t>
         </is>
       </c>
       <c r="B71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Oligo.3 specific MR genes - Oligo.3/Oligo.2: 1.055</t>
         </is>
       </c>
       <c r="G71" t="b">
@@ -2564,28 +2564,28 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CNTNAP2</t>
+          <t>CNTNAP3B</t>
         </is>
       </c>
       <c r="B72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L2_5.2, Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Oligo.3 specific MR genes - Oligo.3/Oligo.2: 1.055</t>
+          <t>Base probe - Inhib.Chandelier, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L6_CT: 1.699</t>
         </is>
       </c>
       <c r="G72" t="b">
@@ -2595,7 +2595,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CNTNAP3B</t>
+          <t>COL12A1</t>
         </is>
       </c>
       <c r="B73" t="b">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2, Inhib.Chandelier</t>
+          <t>Excit.L5_6_NP, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L6_CT: 1.699</t>
+          <t>Base probe - Vasc.VLMC, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.016</t>
         </is>
       </c>
       <c r="G73" t="b">
@@ -2626,28 +2626,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>COL12A1</t>
+          <t>COL16A1</t>
         </is>
       </c>
       <c r="B74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, Vasc.VLMC</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.016</t>
+          <t>Astro.3 specific MR genes - Astro.3/Astro.2: 1.061</t>
         </is>
       </c>
       <c r="G74" t="b">
@@ -2657,7 +2657,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>COL16A1</t>
+          <t>COL21A1</t>
         </is>
       </c>
       <c r="B75" t="b">
@@ -2668,17 +2668,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Astro.3 specific MR genes - Astro.3/Astro.2: 1.061</t>
+          <t>DEG carrier top: Oligo.3 up logFC=2.79</t>
         </is>
       </c>
       <c r="G75" t="b">
@@ -2688,28 +2688,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>COL21A1</t>
+          <t>COL25A1</t>
         </is>
       </c>
       <c r="B76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Sst</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 up</t>
+          <t>Base probe - Inhib.Sst, globl MR genes -  Inhib.Sst/Inhib.Lamp5_Lhx6: 1.643</t>
         </is>
       </c>
       <c r="G76" t="b">
@@ -2719,28 +2719,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>COL25A1</t>
+          <t>COPS9</t>
         </is>
       </c>
       <c r="B77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Inhib.Sst</t>
+          <t>LD~Sp09D02</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst, globl MR genes -  Inhib.Sst/Inhib.Lamp5_Lhx6: 1.643</t>
+          <t>SpD MeanRatio gene: LD~Sp09D02/Inhib~Sp09D09: 1.112</t>
         </is>
       </c>
       <c r="G77" t="b">
@@ -2750,28 +2750,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>COPS9</t>
+          <t>CORO1A</t>
         </is>
       </c>
       <c r="B78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>LD~Sp09D02</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SpD MeanRatio gene: LD~Sp09D02/Inhib~Sp09D09: 1.112</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G78" t="b">
@@ -2781,28 +2781,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CORO1A</t>
+          <t>CPNE4</t>
         </is>
       </c>
       <c r="B79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>DEG of interest: Oligo.3 up logFC=1.87</t>
         </is>
       </c>
       <c r="G79" t="b">
@@ -3246,7 +3246,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DPYSL5</t>
+          <t>DVL2</t>
         </is>
       </c>
       <c r="B94" t="b">
@@ -3257,17 +3257,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oligo.2</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>globl MR genes -  Oligo.2/Oligo.1: 1.557</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
         </is>
       </c>
       <c r="G94" t="b">
@@ -3277,28 +3277,28 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DVL2</t>
+          <t>EFHD1</t>
         </is>
       </c>
       <c r="B95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C95">
         <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G95" t="b">
@@ -3308,7 +3308,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EFHD1</t>
+          <t>EGFR</t>
         </is>
       </c>
       <c r="B96" t="b">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G96" t="b">
@@ -3339,7 +3339,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EGFR</t>
+          <t>ELOVL2</t>
         </is>
       </c>
       <c r="B97" t="b">
@@ -3370,28 +3370,28 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ELOVL2</t>
+          <t>ENC1</t>
         </is>
       </c>
       <c r="B98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C98">
         <v>1</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G98" t="b">
@@ -3401,7 +3401,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ENC1</t>
+          <t>ENSG00000286293</t>
         </is>
       </c>
       <c r="B99" t="b">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>DEG carrier top: Oligo.3 EA_down</t>
         </is>
       </c>
       <c r="G99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ENSG00000229855</t>
+          <t>ENSG00000286438</t>
         </is>
       </c>
       <c r="B100" t="b">
@@ -3443,17 +3443,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L2_5.1 up</t>
+          <t>DEG carrier top: Oligo.3 EA_down</t>
         </is>
       </c>
       <c r="G100" t="b">
@@ -3463,7 +3463,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ENSG00000250453</t>
+          <t>ENSG00000289591</t>
         </is>
       </c>
       <c r="B101" t="b">
@@ -3494,100 +3494,100 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ENSG00000286293</t>
+          <t>ERBB3</t>
         </is>
       </c>
       <c r="B102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base, DEG - carrier, DEG - mediation, DEGs - LR</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo, Oligo.3</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 EA_down</t>
+          <t>Base probe - Oligo, DEG carrier included: Oligo.3 down, mediation gene: outcome Oligo.3, DEG LR interactions: NRG3 -&gt; ERBB3</t>
         </is>
       </c>
       <c r="G102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ENSG00000286438</t>
+          <t>ERBB4</t>
         </is>
       </c>
       <c r="B103" t="b">
         <v>0</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DEG - ancestry, DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo.1</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 down, DEG carrier top: Oligo.3 EA_down</t>
+          <t>Oligo.1 specific Enrich genes t= 5.58</t>
         </is>
       </c>
       <c r="G103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ENSG00000286619</t>
+          <t>ERMN</t>
         </is>
       </c>
       <c r="B104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base, DEG - carrier, DEG - mediation, Marker - SpD</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Inhib.Vip, Oligo, Oligo.3, WM~Sp09D06</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L5.2 down</t>
+          <t>Base probe - Oligo, SpD MeanRatio gene: WM~Sp09D06/L6~Sp09D04: 4.59, DEG carrier included: Oligo.3 down, DEG carrier included: Inhib.Vip down, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ENSG00000287092</t>
+          <t>EXOC7</t>
         </is>
       </c>
       <c r="B105" t="b">
@@ -3598,79 +3598,79 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>OPC.5</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>globl MR genes -  Excit.L5.2/Excit.L5.1: 4.474</t>
+          <t>OPC.5 specific Enrich genes t= 7.33</t>
         </is>
       </c>
       <c r="G105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ENSG00000287422</t>
+          <t>EYA4</t>
         </is>
       </c>
       <c r="B106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 down</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6, globl MR genes -  Inhib.Lamp5_Lhx6/Oligo.2: 6.508</t>
         </is>
       </c>
       <c r="G106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ERBB3</t>
+          <t>FAM171B</t>
         </is>
       </c>
       <c r="B107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, DEGs - LR</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Oligo, Oligo.3</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, DEG carrier included: Oligo.3 down, mediation gene: outcome Oligo.3, DEG LR interactions: NRG3 -&gt; ERBB3</t>
+          <t>Astro.1 specific Enrich genes t= 8.3</t>
         </is>
       </c>
       <c r="G107" t="b">
@@ -3680,28 +3680,28 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ERBB4</t>
+          <t>FASLG</t>
         </is>
       </c>
       <c r="B108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C108">
         <v>1</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Oligo.1</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Oligo.1 specific Enrich genes t= 5.58</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G108" t="b">
@@ -3711,28 +3711,28 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ERMN</t>
+          <t>FBLN1</t>
         </is>
       </c>
       <c r="B109" t="b">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, Marker - SpD</t>
+          <t>Base, DEG - ancestry</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Inhib.Vip, Oligo, Oligo.3, WM~Sp09D06</t>
+          <t>Oligo.3, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, SpD MeanRatio gene: WM~Sp09D06/L6~Sp09D04: 4.59, DEG carrier included: Oligo.3 down, DEG carrier included: Inhib.Vip down, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Vasc.VLMC, DEG Ancestry op: Oligo.3 AA_down-EA_up*</t>
         </is>
       </c>
       <c r="G109" t="b">
@@ -3742,28 +3742,28 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EXOC7</t>
+          <t>FCER1G</t>
         </is>
       </c>
       <c r="B110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C110">
         <v>1</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OPC.5</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>OPC.5 specific Enrich genes t= 7.33</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G110" t="b">
@@ -3773,28 +3773,28 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EYA4</t>
+          <t>FCGR1A</t>
         </is>
       </c>
       <c r="B111" t="b">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6, globl MR genes -  Inhib.Lamp5_Lhx6/Oligo.2: 6.508</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G111" t="b">
@@ -3804,28 +3804,28 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FAM171B</t>
+          <t>FCGR3A</t>
         </is>
       </c>
       <c r="B112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C112">
         <v>1</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Astro.1 specific Enrich genes t= 8.3</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G112" t="b">
@@ -3835,7 +3835,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FASLG</t>
+          <t>FGFR2</t>
         </is>
       </c>
       <c r="B113" t="b">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G113" t="b">
@@ -3866,28 +3866,28 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FBLN1</t>
+          <t>FGFR3</t>
         </is>
       </c>
       <c r="B114" t="b">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Base, DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Oligo.3, Vasc.VLMC</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC, DEG Ancestry op: Oligo.3 AA_down-EA_up*</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="G114" t="b">
@@ -3897,28 +3897,28 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FCER1G</t>
+          <t>FIGN</t>
         </is>
       </c>
       <c r="B115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C115">
         <v>1</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.1</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.4: 1.143</t>
         </is>
       </c>
       <c r="G115" t="b">
@@ -3928,7 +3928,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FCGR1A</t>
+          <t>FILIP1</t>
         </is>
       </c>
       <c r="B116" t="b">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Excit.L6_CT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Excit.L6_CT</t>
         </is>
       </c>
       <c r="G116" t="b">
@@ -3959,7 +3959,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FCGR3A</t>
+          <t>FLT1</t>
         </is>
       </c>
       <c r="B117" t="b">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="G117" t="b">
@@ -3990,28 +3990,28 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FGFR2</t>
+          <t>FOS</t>
         </is>
       </c>
       <c r="B118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C118">
         <v>1</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>DEG carrier top: Oligo.3 up logFC=2.77, DEG of interest: Oligo.3 up logFC=2.77</t>
         </is>
       </c>
       <c r="G118" t="b">
@@ -4021,7 +4021,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FGFR3</t>
+          <t>FSTL4</t>
         </is>
       </c>
       <c r="B119" t="b">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Excit.L4_IT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Base probe - Excit.L4_IT</t>
         </is>
       </c>
       <c r="G119" t="b">
@@ -4052,7 +4052,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FIGN</t>
+          <t>FZD8</t>
         </is>
       </c>
       <c r="B120" t="b">
@@ -4063,17 +4063,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Oligo.1</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.4: 1.143</t>
+          <t>mediation gene: mediator Astro.2</t>
         </is>
       </c>
       <c r="G120" t="b">
@@ -4083,28 +4083,28 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FILIP1</t>
+          <t>GAD1</t>
         </is>
       </c>
       <c r="B121" t="b">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, DEG - mediation, Marker - SpD</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Excit.L6_CT</t>
+          <t>Inhib.Pvalb, Inhib~Sp09D09, Oligo.3</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_CT</t>
+          <t>Base probe - Inhib.Pvalb, SpD MeanRatio gene: Inhib~Sp09D09/LD~Sp09D02: 3.35, SpD Enrich gene t=17.85, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G121" t="b">
@@ -4114,28 +4114,28 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FLT1</t>
+          <t>GAD2</t>
         </is>
       </c>
       <c r="B122" t="b">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, Marker - SpD</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>Inhib.Lamp5_Lhx6, Inhib~Sp09D09, Oligo.3</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6, SpD MeanRatio gene: Inhib~Sp09D09/LD~Sp09D02: 3.308, SpD Enrich gene t=15.34, DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="G122" t="b">
@@ -4145,28 +4145,28 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FOS</t>
+          <t>GAS2L3</t>
         </is>
       </c>
       <c r="B123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C123">
         <v>1</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 up, DEG of interest: Oligo.3 up</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G123" t="b">
@@ -4176,28 +4176,28 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FSTL4</t>
+          <t>GJA1</t>
         </is>
       </c>
       <c r="B124" t="b">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - SpD</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Excit.L4_IT</t>
+          <t>Astro, L1~Sp09D05</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT</t>
+          <t>Base probe - Astro, SpD MeanRatio gene: L1~Sp09D05/LD~Sp09D02: 1.387</t>
         </is>
       </c>
       <c r="G124" t="b">
@@ -4207,28 +4207,28 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FZD8</t>
+          <t>GNLY</t>
         </is>
       </c>
       <c r="B125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C125">
         <v>1</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.2</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G125" t="b">
@@ -4238,28 +4238,28 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GAD1</t>
+          <t>GOLGA7</t>
         </is>
       </c>
       <c r="B126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, Marker - SpD</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb, Inhib~Sp09D09, Oligo.3</t>
+          <t>Oligo.1</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb, SpD MeanRatio gene: Inhib~Sp09D09/LD~Sp09D02: 3.35, SpD Enrich gene t=17.85, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Oligo.1 specific Enrich genes t= 5.54</t>
         </is>
       </c>
       <c r="G126" t="b">
@@ -4269,28 +4269,28 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GAD2</t>
+          <t>GOLGA8A</t>
         </is>
       </c>
       <c r="B127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - SpD</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6, Inhib~Sp09D09, Oligo.3</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6, SpD MeanRatio gene: Inhib~Sp09D09/LD~Sp09D02: 3.308, SpD Enrich gene t=15.34, DEG carrier included: Oligo.3 up</t>
+          <t>DEG carrier top:  Excit.L5.2 up</t>
         </is>
       </c>
       <c r="G127" t="b">
@@ -4300,28 +4300,28 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GAS2L3</t>
+          <t>GPC5-AS1</t>
         </is>
       </c>
       <c r="B128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C128">
         <v>1</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Excit.L5.2 specific MR genes - Excit.L5.2/Excit.L5.1: 13.028</t>
         </is>
       </c>
       <c r="G128" t="b">
@@ -4331,28 +4331,28 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GJA1</t>
+          <t>GPC6</t>
         </is>
       </c>
       <c r="B129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Base, Marker - SpD</t>
+          <t>MOFA - Factor3</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Astro, L1~Sp09D05</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Base probe - Astro, SpD MeanRatio gene: L1~Sp09D05/LD~Sp09D02: 1.387</t>
+          <t>MOFA Oligo.3 Factor3+</t>
         </is>
       </c>
       <c r="G129" t="b">
@@ -4362,28 +4362,28 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GNLY</t>
+          <t>GPM6A</t>
         </is>
       </c>
       <c r="B130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Oligo.3 specific Enrich genes t= 9.66, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G130" t="b">
@@ -4393,28 +4393,28 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GOLGA7</t>
+          <t>GPNMB</t>
         </is>
       </c>
       <c r="B131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C131">
         <v>1</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Oligo.1</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Oligo.1 specific Enrich genes t= 5.54</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G131" t="b">
@@ -4424,28 +4424,28 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GPC5-AS1</t>
+          <t>GPR183</t>
         </is>
       </c>
       <c r="B132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C132">
         <v>1</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Excit.L5.2 specific MR genes - Excit.L5.2/Excit.L5.1: 13.028</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G132" t="b">
@@ -4455,28 +4455,28 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GPC6</t>
+          <t>GPR34</t>
         </is>
       </c>
       <c r="B133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C133">
         <v>1</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>MOFA - Factor3</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>MOFA Oligo.3 Factor3+</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G133" t="b">
@@ -4486,28 +4486,28 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GPM6A</t>
+          <t>GZMA</t>
         </is>
       </c>
       <c r="B134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>DEG - mediation, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Oligo.3 specific Enrich genes t= 9.66, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G134" t="b">
@@ -4517,28 +4517,28 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>GPNMB</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="B135" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C135">
         <v>1</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>DEG carrier top: Oligo.3 AA_down</t>
         </is>
       </c>
       <c r="G135" t="b">
@@ -4548,28 +4548,28 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>GPR149</t>
+          <t>HES1</t>
         </is>
       </c>
       <c r="B136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1</t>
+          <t>Glioblastoma_cancer, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L2_5.1 down</t>
+          <t>Base probe - Glioblastoma_cancer, DEG carrier included: Vasc.VLMC up</t>
         </is>
       </c>
       <c r="G136" t="b">
@@ -4579,7 +4579,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GPR183</t>
+          <t>HHATL</t>
         </is>
       </c>
       <c r="B137" t="b">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G137" t="b">
@@ -4610,7 +4610,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GPR34</t>
+          <t>HILPDA</t>
         </is>
       </c>
       <c r="B138" t="b">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G138" t="b">
@@ -4641,7 +4641,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>GZMA</t>
+          <t>HLA-DMB</t>
         </is>
       </c>
       <c r="B139" t="b">
@@ -4672,28 +4672,28 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>HLA-DQA1</t>
         </is>
       </c>
       <c r="B140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 AA_down</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G140" t="b">
@@ -4703,28 +4703,28 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>HES1</t>
+          <t>HMCN2</t>
         </is>
       </c>
       <c r="B141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer, Vasc.VLMC</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, DEG carrier included: Vasc.VLMC up</t>
+          <t>Excit.L5.2 specific MR genes - Excit.L5.2/Excit.L6b: 13.871</t>
         </is>
       </c>
       <c r="G141" t="b">
@@ -4734,28 +4734,28 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>HHATL</t>
+          <t>HOTAIRM1</t>
         </is>
       </c>
       <c r="B142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C142">
         <v>1</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Excit.L5.2 specific Enrich genes t= 16.54</t>
         </is>
       </c>
       <c r="G142" t="b">
@@ -4765,7 +4765,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>HILPDA</t>
+          <t>HS3ST2</t>
         </is>
       </c>
       <c r="B143" t="b">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Excit.L6_CT</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Excit.L6_CT</t>
         </is>
       </c>
       <c r="G143" t="b">
@@ -4796,7 +4796,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>HLA-DMB</t>
+          <t>HS3ST4</t>
         </is>
       </c>
       <c r="B144" t="b">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Excit.L6_CT</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Excit.L6_CT</t>
         </is>
       </c>
       <c r="G144" t="b">
@@ -4827,7 +4827,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>HLA-DQA1</t>
+          <t>HTR2A</t>
         </is>
       </c>
       <c r="B145" t="b">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Excit.L5_IT</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Excit.L5_IT</t>
         </is>
       </c>
       <c r="G145" t="b">
@@ -4858,28 +4858,28 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>HMCN2</t>
+          <t>HTR2C</t>
         </is>
       </c>
       <c r="B146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Excit.L5.2 specific MR genes - Excit.L5.2/Excit.L6b: 13.871</t>
+          <t>Base probe - Excit.L5_6_NP, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.173</t>
         </is>
       </c>
       <c r="G146" t="b">
@@ -4889,28 +4889,28 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>HOTAIRM1</t>
+          <t>IDH1</t>
         </is>
       </c>
       <c r="B147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C147">
         <v>1</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Excit.L5.2 specific Enrich genes t= 16.54</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G147" t="b">
@@ -4920,7 +4920,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>HS3ST2</t>
+          <t>IDH2</t>
         </is>
       </c>
       <c r="B148" t="b">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Excit.L6_CT</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_CT</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G148" t="b">
@@ -4951,7 +4951,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>HS3ST4</t>
+          <t>IDO1</t>
         </is>
       </c>
       <c r="B149" t="b">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Excit.L6_CT</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_CT</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G149" t="b">
@@ -4982,7 +4982,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>HTR2A</t>
+          <t>IFITM3</t>
         </is>
       </c>
       <c r="B150" t="b">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Excit.L5_IT</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_IT</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G150" t="b">
@@ -5013,7 +5013,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>HTR2C</t>
+          <t>IGFBP3</t>
         </is>
       </c>
       <c r="B151" t="b">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Excit.L6b, Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_6_NP, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.173</t>
+          <t>Base probe - Glioblastoma_cancer, Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 3.37</t>
         </is>
       </c>
       <c r="G151" t="b">
@@ -5044,7 +5044,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>IDH1</t>
+          <t>IGFBP4</t>
         </is>
       </c>
       <c r="B152" t="b">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="G152" t="b">
@@ -5075,28 +5075,28 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IDH2</t>
+          <t>IGFBP5</t>
         </is>
       </c>
       <c r="B153" t="b">
         <v>1</v>
       </c>
       <c r="C153">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Astro.2, Astro.4, Glioblastoma_cancer, Oligo.3</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Glioblastoma_cancer, Astro.4 specific MR gene - Astro.4/Astro.5: 4.236, DEG carrier included: Astro.2 down, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G153" t="b">
@@ -5106,28 +5106,28 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>IDO1</t>
+          <t>IKZF1</t>
         </is>
       </c>
       <c r="B154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C154">
         <v>1</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>DEG carrier top: Oligo.3 up logFC=2.75</t>
         </is>
       </c>
       <c r="G154" t="b">
@@ -5137,28 +5137,28 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>IFITM3</t>
+          <t>IL6ST</t>
         </is>
       </c>
       <c r="B155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C155">
         <v>1</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>mediation gene: mediator Astro.3</t>
         </is>
       </c>
       <c r="G155" t="b">
@@ -5168,28 +5168,28 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>IGFBP3</t>
+          <t>IL7R</t>
         </is>
       </c>
       <c r="B156" t="b">
         <v>1</v>
       </c>
       <c r="C156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Excit.L6b, Glioblastoma_cancer</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 3.37</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G156" t="b">
@@ -5199,28 +5199,28 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>IGFBP4</t>
+          <t>ITGA8</t>
         </is>
       </c>
       <c r="B157" t="b">
         <v>1</v>
       </c>
       <c r="C157">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Excit.L5_6_NP, OPC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - OPC, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6b: 3.576</t>
         </is>
       </c>
       <c r="G157" t="b">
@@ -5230,28 +5230,28 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>IGFBP5</t>
+          <t>ITGAM</t>
         </is>
       </c>
       <c r="B158" t="b">
         <v>1</v>
       </c>
       <c r="C158">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Astro.2, Astro.4, Glioblastoma_cancer, Oligo.3</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, Astro.4 specific MR gene - Astro.4/Astro.5: 4.236, DEG carrier included: Astro.2 down, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G158" t="b">
@@ -5261,7 +5261,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>IKZF1</t>
+          <t>ITGAV</t>
         </is>
       </c>
       <c r="B159" t="b">
@@ -5272,17 +5272,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo.2</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 up</t>
+          <t>Oligo.2 specific MR genes - Oligo.2/Oligo.1: 1.663</t>
         </is>
       </c>
       <c r="G159" t="b">
@@ -5292,28 +5292,28 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>IL6ST</t>
+          <t>ITGAX</t>
         </is>
       </c>
       <c r="B160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C160">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base, DEG - carrier, Marker - cell type global</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Micro, Micro.1, Oligo.3</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.3</t>
+          <t>Base probe - Micro, globl MR genes -  Micro.1/Micro.4: 1.044, DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="G160" t="b">
@@ -5323,7 +5323,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>IL7R</t>
+          <t>ITGB2</t>
         </is>
       </c>
       <c r="B161" t="b">
@@ -5354,28 +5354,28 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ITGA8</t>
+          <t>KAT2A</t>
         </is>
       </c>
       <c r="B162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C162">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, OPC</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Base probe - OPC, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6b: 3.576</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up*-EA_down</t>
         </is>
       </c>
       <c r="G162" t="b">
@@ -5385,28 +5385,28 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ITGAM</t>
+          <t>KCND2</t>
         </is>
       </c>
       <c r="B163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C163">
         <v>1</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Oligo.3 specific Enrich genes t= 9.2</t>
         </is>
       </c>
       <c r="G163" t="b">
@@ -5416,28 +5416,28 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ITGAV</t>
+          <t>KCNH5</t>
         </is>
       </c>
       <c r="B164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Oligo.2</t>
+          <t>Excit.L6_CT</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Oligo.2 specific MR genes - Oligo.2/Oligo.1: 1.663</t>
+          <t>Base probe - Excit.L6_CT, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L6b: 1.583</t>
         </is>
       </c>
       <c r="G164" t="b">
@@ -5447,28 +5447,28 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ITGAX</t>
+          <t>KCNJ3</t>
         </is>
       </c>
       <c r="B165" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C165">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type global</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Micro, Micro.1, Oligo.3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Base probe - Micro, globl MR genes -  Micro.1/Micro.4: 1.044, DEG carrier included: Oligo.3 up</t>
+          <t>Oligo.3 specific Enrich genes t= 9.5</t>
         </is>
       </c>
       <c r="G165" t="b">
@@ -5478,28 +5478,28 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ITGB2</t>
+          <t>KIT</t>
         </is>
       </c>
       <c r="B166" t="b">
         <v>1</v>
       </c>
       <c r="C166">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type global, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Excit.L6_CT, Inhib.Lamp5_Lhx6, Proliferation</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Proliferation, globl MR genes -  Inhib.Lamp5_Lhx6/Inhib.Vip: 3.628, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L5_6_NP: 7.823</t>
         </is>
       </c>
       <c r="G166" t="b">
@@ -5509,28 +5509,28 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>KAT2A</t>
+          <t>KLF2</t>
         </is>
       </c>
       <c r="B167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C167">
         <v>1</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up*-EA_down</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G167" t="b">
@@ -5540,28 +5540,28 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>KCND2</t>
+          <t>KLF4</t>
         </is>
       </c>
       <c r="B168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C168">
         <v>1</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Oligo.3 specific Enrich genes t= 9.2</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G168" t="b">
@@ -5571,28 +5571,28 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>KCNH5</t>
+          <t>KLK6</t>
         </is>
       </c>
       <c r="B169" t="b">
         <v>1</v>
       </c>
       <c r="C169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Excit.L6_CT</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_CT, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L6b: 1.583</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G169" t="b">
@@ -5602,28 +5602,28 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>KCNJ3</t>
+          <t>KLRB1</t>
         </is>
       </c>
       <c r="B170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C170">
         <v>1</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Oligo.3 specific Enrich genes t= 9.5</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G170" t="b">
@@ -5633,28 +5633,28 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>KIT</t>
+          <t>LAMA2</t>
         </is>
       </c>
       <c r="B171" t="b">
         <v>1</v>
       </c>
       <c r="C171">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global, Marker - cell type specific</t>
+          <t>Base, DEG - carrier, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Excit.L6_CT, Inhib.Lamp5_Lhx6, Proliferation</t>
+          <t>Astro.2, Excit.L2_5.2, Oligo.4, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Base probe - Proliferation, globl MR genes -  Inhib.Lamp5_Lhx6/Inhib.Vip: 3.628, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L5_6_NP: 7.823</t>
+          <t>Base probe - Vasc.VLMC, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5.2: 2.04, Oligo.4 specific Enrich genes t= 4.39, DEG carrier included: Astro.2 down</t>
         </is>
       </c>
       <c r="G171" t="b">
@@ -5664,28 +5664,28 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>KLF2</t>
+          <t>LAMP5</t>
         </is>
       </c>
       <c r="B172" t="b">
         <v>1</v>
       </c>
       <c r="C172">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - SpD</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Inhib.Lamp5_Lhx6, L2.3~Sp09D01</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6, SpD MeanRatio gene: L2.3~Sp09D01/LD~Sp09D02: 2.406</t>
         </is>
       </c>
       <c r="G172" t="b">
@@ -5695,28 +5695,28 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>KLF4</t>
+          <t>LERFS</t>
         </is>
       </c>
       <c r="B173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>DEG carrier top: Oligo.3 down logFC=-1.39</t>
         </is>
       </c>
       <c r="G173" t="b">
@@ -5726,7 +5726,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>KLK6</t>
+          <t>LHX6</t>
         </is>
       </c>
       <c r="B174" t="b">
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Base probe - Inhib.Chandelier</t>
         </is>
       </c>
       <c r="G174" t="b">
@@ -5757,28 +5757,28 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>KLRB1</t>
+          <t>LINC00472</t>
         </is>
       </c>
       <c r="B175" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C175">
         <v>1</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>DEG Ancestry op: Oligo.3 AA_down-EA_up*</t>
         </is>
       </c>
       <c r="G175" t="b">
@@ -5788,28 +5788,28 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>LAMA2</t>
+          <t>LINC00486</t>
         </is>
       </c>
       <c r="B176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C176">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type specific</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Astro.2, Excit.L2_5.2, Oligo.4, Vasc.VLMC</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5.2: 2.04, Oligo.4 specific Enrich genes t= 4.39, DEG carrier included: Astro.2 down</t>
+          <t>DEG carrier top:  Excit.L5.2 up</t>
         </is>
       </c>
       <c r="G176" t="b">
@@ -5819,28 +5819,28 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>LAMP5</t>
+          <t>LINC00609</t>
         </is>
       </c>
       <c r="B177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Base, Marker - SpD</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6, L2.3~Sp09D01</t>
+          <t>Oligo.2</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6, SpD MeanRatio gene: L2.3~Sp09D01/LD~Sp09D02: 2.406</t>
+          <t>Oligo.2 specific Enrich genes t= 10.42</t>
         </is>
       </c>
       <c r="G177" t="b">
@@ -5850,7 +5850,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>LERFS</t>
+          <t>LINC00706</t>
         </is>
       </c>
       <c r="B178" t="b">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 down</t>
+          <t>DEG carrier top: Oligo.3 AA_down</t>
         </is>
       </c>
       <c r="G178" t="b">
@@ -5881,28 +5881,28 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>LHX6</t>
+          <t>LINC01877</t>
         </is>
       </c>
       <c r="B179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type global, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Inhib.Chandelier</t>
+          <t>Oligo.2</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier</t>
+          <t>globl MR genes -  Oligo.2/Oligo.1: 1.743, Oligo.2 specific MR genes - Oligo.2/Oligo.1: 1.743</t>
         </is>
       </c>
       <c r="G179" t="b">
@@ -5912,7 +5912,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>LINC00326</t>
+          <t>LINC02752</t>
         </is>
       </c>
       <c r="B180" t="b">
@@ -5923,17 +5923,17 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L2_5.1 up</t>
+          <t>globl MR genes -  Excit.L5.2/Excit.L2_5.2: 10.797</t>
         </is>
       </c>
       <c r="G180" t="b">
@@ -5943,7 +5943,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>LINC00472</t>
+          <t>LINGO2</t>
         </is>
       </c>
       <c r="B181" t="b">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_down-EA_up*</t>
+          <t>Oligo.3 specific Enrich genes t= 9.09</t>
         </is>
       </c>
       <c r="G181" t="b">
@@ -5974,7 +5974,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>LINC00609</t>
+          <t>LMO3</t>
         </is>
       </c>
       <c r="B182" t="b">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Oligo.2</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Oligo.2 specific Enrich genes t= 10.42</t>
+          <t>Astro.1 specific Enrich genes t= 8.73</t>
         </is>
       </c>
       <c r="G182" t="b">
@@ -6005,28 +6005,28 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>LINC00706</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C183">
         <v>1</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 AA_down</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G183" t="b">
@@ -6036,7 +6036,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>LINC01360</t>
+          <t>LPAR1</t>
         </is>
       </c>
       <c r="B184" t="b">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Excit.L2_5.1</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L5.2 up</t>
+          <t>DEG carrier top:  Excit.L2_5.1 down</t>
         </is>
       </c>
       <c r="G184" t="b">
@@ -6067,28 +6067,28 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>LINC01877</t>
+          <t>LRRK1</t>
         </is>
       </c>
       <c r="B185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Marker - cell type global, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Oligo.2</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>globl MR genes -  Oligo.2/Oligo.1: 1.743, Oligo.2 specific MR genes - Oligo.2/Oligo.1: 1.743</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G185" t="b">
@@ -6098,28 +6098,28 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>LINC02752</t>
+          <t>LRRK2</t>
         </is>
       </c>
       <c r="B186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C186">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base, DEG - carrier, DEG - mediation</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Oligo.3, OPC</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>globl MR genes -  Excit.L5.2/Excit.L2_5.2: 10.797</t>
+          <t>Base probe - OPC, DEG carrier included: Oligo.3 up, DEG of interest: Oligo.3 up logFC=1.61, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G186" t="b">
@@ -6129,7 +6129,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>LINGO2</t>
+          <t>LURAP1L-AS1</t>
         </is>
       </c>
       <c r="B187" t="b">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Oligo.3 specific Enrich genes t= 9.09</t>
+          <t>DEG carrier top: Oligo.3 down logFC=-1.48</t>
         </is>
       </c>
       <c r="G187" t="b">
@@ -6160,28 +6160,28 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>LMO3</t>
+          <t>LY86</t>
         </is>
       </c>
       <c r="B188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Astro.1 specific Enrich genes t= 8.73</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G188" t="b">
@@ -6191,7 +6191,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>LYPD6</t>
         </is>
       </c>
       <c r="B189" t="b">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="G189" t="b">
@@ -6222,7 +6222,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>LRRK1</t>
+          <t>LYPD6B</t>
         </is>
       </c>
       <c r="B190" t="b">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Inhib.Sncg</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Inhib.Sncg</t>
         </is>
       </c>
       <c r="G190" t="b">
@@ -6253,28 +6253,28 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>LRRK2</t>
+          <t>LYVE1</t>
         </is>
       </c>
       <c r="B191" t="b">
         <v>1</v>
       </c>
       <c r="C191">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Oligo.3, OPC</t>
+          <t>Macro, Micro</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Base probe - OPC, DEG carrier included: Oligo.3 up, DEG of interest: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Micro, globl MR genes -  Macro/Micro.4: 2.653</t>
         </is>
       </c>
       <c r="G191" t="b">
@@ -6284,28 +6284,28 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>LURAP1L-AS1</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="B192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C192">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base, DEG - carrier, DEG - mediation</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo, Oligo.3</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 down</t>
+          <t>Base probe - Oligo, DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.77, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G192" t="b">
@@ -6315,28 +6315,28 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LY86</t>
+          <t>MAGED2</t>
         </is>
       </c>
       <c r="B193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
         </is>
       </c>
       <c r="G193" t="b">
@@ -6346,28 +6346,28 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LYPD6</t>
+          <t>MAL</t>
         </is>
       </c>
       <c r="B194" t="b">
         <v>1</v>
       </c>
       <c r="C194">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6</t>
+          <t>Oligo, Oligo.3</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6</t>
+          <t>Base probe - Oligo, DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.76</t>
         </is>
       </c>
       <c r="G194" t="b">
@@ -6377,28 +6377,28 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LYPD6B</t>
+          <t>MAPT</t>
         </is>
       </c>
       <c r="B195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C195">
         <v>1</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Inhib.Sncg</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sncg</t>
+          <t>DEG of interest: Oligo.3 down logFC=-0.56</t>
         </is>
       </c>
       <c r="G195" t="b">
@@ -6408,28 +6408,28 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>LYVE1</t>
+          <t>MBP</t>
         </is>
       </c>
       <c r="B196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C196">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>DEG - carrier, DEG - mediation, Marker - SpD</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Macro, Micro</t>
+          <t>Oligo.3, WM.uf~Sp09D07</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Base probe - Micro, globl MR genes -  Macro/Micro.4: 2.653</t>
+          <t>SpD Enrich gene t=6.53, DEG of interest: Oligo.3 down logFC=-0.69, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G196" t="b">
@@ -6439,7 +6439,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>MCTP2</t>
         </is>
       </c>
       <c r="B197" t="b">
@@ -6450,17 +6450,17 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation</t>
+          <t>Base, Marker - cell type global, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Oligo, Oligo.3</t>
+          <t>Excit.L6b, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Vasc.VLMC, globl MR genes -  Excit.L6b/Vasc.VLMC: 3.051, Excit.L6b specific MR gene - Excit.L6b/Excit.L5_6_NP: 5.834</t>
         </is>
       </c>
       <c r="G197" t="b">
@@ -6470,7 +6470,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MAGED2</t>
+          <t>MEG3</t>
         </is>
       </c>
       <c r="B198" t="b">
@@ -6481,17 +6481,17 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>OPC.5</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
+          <t>OPC.5 specific MR genes - OPC.5/OPC.2: 1.019</t>
         </is>
       </c>
       <c r="G198" t="b">
@@ -6501,28 +6501,28 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MAL</t>
+          <t>MEIS2</t>
         </is>
       </c>
       <c r="B199" t="b">
         <v>1</v>
       </c>
       <c r="C199">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Oligo, Oligo.3</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="G199" t="b">
@@ -6532,28 +6532,28 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>MAPT</t>
+          <t>MEPE</t>
         </is>
       </c>
       <c r="B200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Pvalb</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>DEG of interest: Oligo.3 down</t>
+          <t>Base probe - Inhib.Pvalb</t>
         </is>
       </c>
       <c r="G200" t="b">
@@ -6563,28 +6563,28 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MBP</t>
+          <t>MGST1</t>
         </is>
       </c>
       <c r="B201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C201">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>DEG - carrier, DEG - mediation, Marker - SpD</t>
+          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Oligo.3, WM.uf~Sp09D07</t>
+          <t>Excit.L6b, Glioblastoma_cancer, Oligo.3</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SpD Enrich gene t=6.53, DEG of interest: Oligo.3 down, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Glioblastoma_cancer, Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 1.869, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G201" t="b">
@@ -6594,28 +6594,28 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>MCTP2</t>
+          <t>MIAT</t>
         </is>
       </c>
       <c r="B202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C202">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global, Marker - cell type specific</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Excit.L6b, Vasc.VLMC</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC, globl MR genes -  Excit.L6b/Vasc.VLMC: 3.051, Excit.L6b specific MR gene - Excit.L6b/Excit.L5_6_NP: 5.834</t>
+          <t>DEG carrier top: Oligo.3 AA_up</t>
         </is>
       </c>
       <c r="G202" t="b">
@@ -6625,28 +6625,28 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>MEG3</t>
+          <t>MKI67</t>
         </is>
       </c>
       <c r="B203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C203">
         <v>1</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>OPC.5</t>
+          <t>Proliferation</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>OPC.5 specific MR genes - OPC.5/OPC.2: 1.019</t>
+          <t>Base probe - Proliferation</t>
         </is>
       </c>
       <c r="G203" t="b">
@@ -6656,28 +6656,28 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MEIS2</t>
+          <t>MMD2</t>
         </is>
       </c>
       <c r="B204" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C204">
         <v>1</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Astro.2 specific MR genes - Astro.2/Astro.5: 1.004</t>
         </is>
       </c>
       <c r="G204" t="b">
@@ -6687,28 +6687,28 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>MEPE</t>
+          <t>MOBP</t>
         </is>
       </c>
       <c r="B205" t="b">
         <v>1</v>
       </c>
       <c r="C205">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, Marker - SpD</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb</t>
+          <t>Astro.2, Oligo, WM.uf~Sp09D07, WM~Sp09D06</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb</t>
+          <t>Base probe - Oligo, SpD Enrich gene t=6.03, SpD MeanRatio gene: WM~Sp09D06/WM.uf~Sp09D07: 3.219, DEG carrier included: Astro.2 down</t>
         </is>
       </c>
       <c r="G205" t="b">
@@ -6718,28 +6718,28 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>MGST1</t>
+          <t>MOG</t>
         </is>
       </c>
       <c r="B206" t="b">
         <v>1</v>
       </c>
       <c r="C206">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Excit.L6b, Glioblastoma_cancer, Oligo.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 1.869, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G206" t="b">
@@ -6749,28 +6749,28 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>MIAT</t>
+          <t>MS4A6A</t>
         </is>
       </c>
       <c r="B207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C207">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME, Macro</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 AA_up</t>
+          <t>Base probe - Glioblastoma_TME, globl MR genes -  Macro/Micro.3: 4.29</t>
         </is>
       </c>
       <c r="G207" t="b">
@@ -6780,7 +6780,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>MIR4280HG</t>
+          <t>MT-CO3</t>
         </is>
       </c>
       <c r="B208" t="b">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -6801,38 +6801,38 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 down</t>
+          <t>Oligo.3 specific MR genes - Oligo.3/Oligo.4: 1.141</t>
         </is>
       </c>
       <c r="G208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MKI67</t>
+          <t>MT-CYB</t>
         </is>
       </c>
       <c r="B209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C209">
         <v>1</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Proliferation</t>
+          <t>Excit.L2_5.1</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Base probe - Proliferation</t>
+          <t>Excit.L2_5.1 specific MR genes - Excit.L2_5.1/Excit.L6b: 1.175</t>
         </is>
       </c>
       <c r="G209" t="b">
@@ -6842,7 +6842,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>MMD2</t>
+          <t>MT-ND1</t>
         </is>
       </c>
       <c r="B210" t="b">
@@ -6858,12 +6858,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Excit.L2_5.1</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Astro.2 specific MR genes - Astro.2/Astro.5: 1.004</t>
+          <t>Excit.L2_5.1 specific MR genes - Excit.L2_5.1/Excit.L6b: 1.201</t>
         </is>
       </c>
       <c r="G210" t="b">
@@ -6873,28 +6873,28 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>MOBP</t>
+          <t>MT-ND4</t>
         </is>
       </c>
       <c r="B211" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C211">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - SpD</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Astro.2, Oligo, WM.uf~Sp09D07, WM~Sp09D06</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, SpD Enrich gene t=6.03, SpD MeanRatio gene: WM~Sp09D06/WM.uf~Sp09D07: 3.219, DEG carrier included: Astro.2 down</t>
+          <t>DEG carrier top:  Excit.L5.2 down</t>
         </is>
       </c>
       <c r="G211" t="b">
@@ -6904,28 +6904,28 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>MOG</t>
+          <t>MTX2</t>
         </is>
       </c>
       <c r="B212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C212">
         <v>1</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Oligo.2</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Oligo.2 specific Enrich genes t= 11.38</t>
         </is>
       </c>
       <c r="G212" t="b">
@@ -6935,28 +6935,28 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>MYO16</t>
         </is>
       </c>
       <c r="B213" t="b">
         <v>1</v>
       </c>
       <c r="C213">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME, Macro</t>
+          <t>Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME, globl MR genes -  Macro/Micro.3: 4.29</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="G213" t="b">
@@ -6966,28 +6966,28 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>MT-CO3</t>
+          <t>MYO5B</t>
         </is>
       </c>
       <c r="B214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C214">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Pvalb</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Oligo.3 specific MR genes - Oligo.3/Oligo.4: 1.141</t>
+          <t>Base probe - Inhib.Pvalb, globl MR genes -  Inhib.Pvalb/Inhib.Sst: 2.178</t>
         </is>
       </c>
       <c r="G214" t="b">
@@ -6997,28 +6997,28 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MT-CYB</t>
+          <t>MYRF</t>
         </is>
       </c>
       <c r="B215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C215">
         <v>1</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1 specific MR genes - Excit.L2_5.1/Excit.L6b: 1.175</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G215" t="b">
@@ -7028,7 +7028,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>MT-ND1</t>
+          <t>NAP1L3</t>
         </is>
       </c>
       <c r="B216" t="b">
@@ -7039,17 +7039,17 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1 specific MR genes - Excit.L2_5.1/Excit.L6b: 1.201</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G216" t="b">
@@ -7059,28 +7059,28 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>MTX2</t>
+          <t>NCSTN</t>
         </is>
       </c>
       <c r="B217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C217">
         <v>1</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Oligo.2</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Oligo.2 specific Enrich genes t= 11.38</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G217" t="b">
@@ -7090,28 +7090,28 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>MYO16</t>
+          <t>NDST4</t>
         </is>
       </c>
       <c r="B218" t="b">
         <v>1</v>
       </c>
       <c r="C218">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6</t>
+          <t>Excit.L5.2, Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6</t>
+          <t>Base probe - Inhib.Sst_Chold, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L5.1: 3.841</t>
         </is>
       </c>
       <c r="G218" t="b">
@@ -7121,28 +7121,28 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MYO5B</t>
+          <t>NES</t>
         </is>
       </c>
       <c r="B219" t="b">
         <v>1</v>
       </c>
       <c r="C219">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb, globl MR genes -  Inhib.Pvalb/Inhib.Sst: 2.178</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="G219" t="b">
@@ -7152,28 +7152,28 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MYRF</t>
+          <t>NETO1</t>
         </is>
       </c>
       <c r="B220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C220">
         <v>1</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>mediation gene: mediator Astro.2</t>
         </is>
       </c>
       <c r="G220" t="b">
@@ -7183,28 +7183,28 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>NAP1L3</t>
+          <t>NKG7</t>
         </is>
       </c>
       <c r="B221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C221">
         <v>1</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G221" t="b">
@@ -7214,28 +7214,28 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>NCSTN</t>
+          <t>NLGN1</t>
         </is>
       </c>
       <c r="B222" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C222">
         <v>1</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>DEG LR interactions: NLGN1 -&gt; NRXN1,NLGN1 -&gt; NRXN3,NRXN1 -&gt; NLGN1,NRXN3 -&gt; NLGN1</t>
         </is>
       </c>
       <c r="G222" t="b">
@@ -7245,28 +7245,28 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>NDST4</t>
+          <t>NNAT</t>
         </is>
       </c>
       <c r="B223" t="b">
         <v>1</v>
       </c>
       <c r="C223">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base, Marker - cell type specific, Marker - SpD</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Excit.L5.2, Inhib.Sst_Chold</t>
+          <t>Excit.L6b, Glioblastoma_cancer, L6~Sp09D04</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L5.1: 3.841</t>
+          <t>Base probe - Glioblastoma_cancer, Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 1.661, SpD MeanRatio gene: L6~Sp09D04/L2.3~Sp09D01: 1.542, SpD Enrich gene t=10.01</t>
         </is>
       </c>
       <c r="G223" t="b">
@@ -7276,7 +7276,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>NES</t>
+          <t>NOTCH1</t>
         </is>
       </c>
       <c r="B224" t="b">
@@ -7292,12 +7292,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="G224" t="b">
@@ -7307,28 +7307,28 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>NETO1</t>
+          <t>NPFFR2</t>
         </is>
       </c>
       <c r="B225" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C225">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base, Marker - cell type global, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Excit.L6_CT, Excit.L6b</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.2</t>
+          <t>Base probe - Excit.L6b, globl MR genes -  Excit.L6_CT/Excit.L2_5.1: 3.469, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2_5.1: 3.469</t>
         </is>
       </c>
       <c r="G225" t="b">
@@ -7338,28 +7338,28 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>NKG7</t>
+          <t>NPNT</t>
         </is>
       </c>
       <c r="B226" t="b">
         <v>1</v>
       </c>
       <c r="C226">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type global, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Excit.L2_5.2, Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Inhib.Chandelier, globl MR genes -  Inhib.Chandelier/Excit.L2_5.2: 3.131, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5_6_NP: 6.062</t>
         </is>
       </c>
       <c r="G226" t="b">
@@ -7369,7 +7369,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>NKX6-2</t>
+          <t>NPTXR</t>
         </is>
       </c>
       <c r="B227" t="b">
@@ -7380,17 +7380,17 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>MOFA - Factor3</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>MOFA Oligo.3 Factor3-</t>
+          <t>mediation gene: mediator Astro.1</t>
         </is>
       </c>
       <c r="G227" t="b">
@@ -7400,28 +7400,28 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>NLGN1</t>
+          <t>NPY1R</t>
         </is>
       </c>
       <c r="B228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NLGN1 -&gt; NRXN1,NLGN1 -&gt; NRXN3,NRXN1 -&gt; NLGN1,NRXN3 -&gt; NLGN1</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G228" t="b">
@@ -7431,28 +7431,28 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>NNAT</t>
+          <t>NR2F2</t>
         </is>
       </c>
       <c r="B229" t="b">
         <v>1</v>
       </c>
       <c r="C229">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific, Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Excit.L6b, Glioblastoma_cancer, L6~Sp09D04</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 1.661, SpD MeanRatio gene: L6~Sp09D04/L2.3~Sp09D01: 1.542, SpD Enrich gene t=10.01</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="G229" t="b">
@@ -7462,28 +7462,28 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>NOTCH1</t>
+          <t>NR4A2</t>
         </is>
       </c>
       <c r="B230" t="b">
         <v>1</v>
       </c>
       <c r="C230">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>Glioblastoma_TME, Oligo.3</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>Base probe - Glioblastoma_TME, DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="G230" t="b">
@@ -7493,28 +7493,28 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>NPFFR2</t>
+          <t>NRG3</t>
         </is>
       </c>
       <c r="B231" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C231">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global, Marker - cell type specific</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Excit.L6_CT, Excit.L6b</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6b, globl MR genes -  Excit.L6_CT/Excit.L2_5.1: 3.469, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2_5.1: 3.469</t>
+          <t>DEG LR interactions: NRG3 -&gt; ERBB3</t>
         </is>
       </c>
       <c r="G231" t="b">
@@ -7524,7 +7524,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>NPNT</t>
+          <t>NRP1</t>
         </is>
       </c>
       <c r="B232" t="b">
@@ -7535,17 +7535,17 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global, Marker - cell type specific</t>
+          <t>Base, DEG - carrier, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2, Inhib.Chandelier</t>
+          <t>Excit.L6_CT, Macro, Vasc.Endo</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier, globl MR genes -  Inhib.Chandelier/Excit.L2_5.2: 3.131, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5_6_NP: 6.062</t>
+          <t>Base probe - Vasc.Endo, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2: 1.859, DEG carrier included: Macro down</t>
         </is>
       </c>
       <c r="G232" t="b">
@@ -7555,7 +7555,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>NPTXR</t>
+          <t>NRXN1</t>
         </is>
       </c>
       <c r="B233" t="b">
@@ -7566,17 +7566,17 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.1</t>
+          <t>DEG LR interactions: NLGN1 -&gt; NRXN1,NLGN4X -&gt; NRXN1,NRXN1 -&gt; NLGN1,NXPH1 -&gt; NRXN1</t>
         </is>
       </c>
       <c r="G233" t="b">
@@ -7586,28 +7586,28 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>NPY1R</t>
+          <t>NRXN3</t>
         </is>
       </c>
       <c r="B234" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C234">
         <v>1</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>DEG LR interactions: NLGN1 -&gt; NRXN3,NRXN3 -&gt; NLGN1,NXPH1 -&gt; NRXN3</t>
         </is>
       </c>
       <c r="G234" t="b">
@@ -7617,28 +7617,28 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>NR2F2</t>
+          <t>NTNG1</t>
         </is>
       </c>
       <c r="B235" t="b">
         <v>1</v>
       </c>
       <c r="C235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Astro.4, Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6, Astro.4 specific MR gene - Astro.4/Astro.2: 2.001</t>
         </is>
       </c>
       <c r="G235" t="b">
@@ -7648,28 +7648,28 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>NR4A2</t>
+          <t>NTNG2</t>
         </is>
       </c>
       <c r="B236" t="b">
         <v>1</v>
       </c>
       <c r="C236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME, Oligo.3</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME, DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G236" t="b">
@@ -7679,18 +7679,18 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>NRG3</t>
+          <t>NTRK3</t>
         </is>
       </c>
       <c r="B237" t="b">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>DEGs - LR, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NRG3 -&gt; ERBB3</t>
+          <t>Oligo.3 specific Enrich genes t= 9.07, DEG LR interactions: NTRK3 -&gt; PTPRD</t>
         </is>
       </c>
       <c r="G237" t="b">
@@ -7710,28 +7710,28 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>NRP1</t>
+          <t>NWD2</t>
         </is>
       </c>
       <c r="B238" t="b">
         <v>1</v>
       </c>
       <c r="C238">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Excit.L6_CT, Macro, Vasc.Endo</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2: 1.859, DEG carrier included: Macro down</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G238" t="b">
@@ -7741,28 +7741,28 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>NRXN1</t>
+          <t>NXPH2</t>
         </is>
       </c>
       <c r="B239" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L5_6_NP, Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NLGN1 -&gt; NRXN1,NLGN4X -&gt; NRXN1,NRXN1 -&gt; NLGN1,NXPH1 -&gt; NRXN1</t>
+          <t>Base probe - Inhib.Sst_Chold, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 16.109</t>
         </is>
       </c>
       <c r="G239" t="b">
@@ -7772,28 +7772,28 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>NRXN3</t>
+          <t>OLIG1</t>
         </is>
       </c>
       <c r="B240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NLGN1 -&gt; NRXN3,NRXN3 -&gt; NLGN1,NXPH1 -&gt; NRXN3</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="G240" t="b">
@@ -7803,7 +7803,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>NTNG1</t>
+          <t>OLIG2</t>
         </is>
       </c>
       <c r="B241" t="b">
@@ -7814,17 +7814,17 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Astro.4, Inhib.Lamp5_Lhx6</t>
+          <t>OPC, OPC.4</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6, Astro.4 specific MR gene - Astro.4/Astro.2: 2.001</t>
+          <t>Base probe - OPC, globl MR genes -  OPC.4/OPC.1: 1.089</t>
         </is>
       </c>
       <c r="G241" t="b">
@@ -7834,28 +7834,28 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>NTNG2</t>
+          <t>OPALIN</t>
         </is>
       </c>
       <c r="B242" t="b">
         <v>1</v>
       </c>
       <c r="C242">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, Marker - cell type global, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Astro.3, Excit.L2_5.1, Oligo, Oligo.1, Oligo.3</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Oligo, globl MR genes -  Oligo.1/Oligo.4: 1.2, Excit.L2_5.1 specific Enrich genes t= 7.46, Oligo.1 specific MR genes - Oligo.1/Oligo.4: 1.2, Oligo.1 specific Enrich genes t= 5.2, DEG carrier included: Astro.3 down, DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.65</t>
         </is>
       </c>
       <c r="G242" t="b">
@@ -7865,28 +7865,28 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>NTRK3</t>
+          <t>OST4</t>
         </is>
       </c>
       <c r="B243" t="b">
         <v>0</v>
       </c>
       <c r="C243">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>DEGs - LR, Marker - cell type specific</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>LD~Sp09D02</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Oligo.3 specific Enrich genes t= 9.07, DEG LR interactions: NTRK3 -&gt; PTPRD</t>
+          <t>SpD MeanRatio gene: LD~Sp09D02/L2.3~Sp09D01: 1.109</t>
         </is>
       </c>
       <c r="G243" t="b">
@@ -7896,7 +7896,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>NWD2</t>
+          <t>OTOGL</t>
         </is>
       </c>
       <c r="B244" t="b">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Excit.L4_IT</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Excit.L4_IT</t>
         </is>
       </c>
       <c r="G244" t="b">
@@ -7927,7 +7927,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>NXPH2</t>
+          <t>P2RY12</t>
         </is>
       </c>
       <c r="B245" t="b">
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, Inhib.Sst_Chold</t>
+          <t>Macro, Micro</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 16.109</t>
+          <t>Base probe - Micro, DEG carrier included: Macro down</t>
         </is>
       </c>
       <c r="G245" t="b">
@@ -7958,7 +7958,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>OLIG1</t>
+          <t>P2RY13</t>
         </is>
       </c>
       <c r="B246" t="b">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G246" t="b">
@@ -7989,28 +7989,28 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>OLIG2</t>
+          <t>PABPN1</t>
         </is>
       </c>
       <c r="B247" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C247">
         <v>2</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>OPC, OPC.4</t>
+          <t>Astro.3, Excit.L2_5.1</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Base probe - OPC, globl MR genes -  OPC.4/OPC.1: 1.089</t>
+          <t>Astro.3 specific MR genes - Astro.3/Astro.1: 1.046, Excit.L2_5.1 specific Enrich genes t= 9.16</t>
         </is>
       </c>
       <c r="G247" t="b">
@@ -8020,28 +8020,28 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>OPALIN</t>
+          <t>PAX6</t>
         </is>
       </c>
       <c r="B248" t="b">
         <v>1</v>
       </c>
       <c r="C248">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type global, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Astro.3, Excit.L2_5.1, Oligo, Oligo.1, Oligo.3</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, globl MR genes -  Oligo.1/Oligo.4: 1.2, Excit.L2_5.1 specific Enrich genes t= 7.46, Oligo.1 specific MR genes - Oligo.1/Oligo.4: 1.2, Oligo.1 specific Enrich genes t= 5.2, DEG carrier included: Astro.3 down, DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="G248" t="b">
@@ -8051,7 +8051,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>OST4</t>
+          <t>PCDH9-AS2</t>
         </is>
       </c>
       <c r="B249" t="b">
@@ -8062,17 +8062,17 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>LD~Sp09D02</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SpD MeanRatio gene: LD~Sp09D02/L2.3~Sp09D01: 1.109</t>
+          <t>Astro.1 specific MR genes - Astro.1/Astro.3: 1.486</t>
         </is>
       </c>
       <c r="G249" t="b">
@@ -8082,7 +8082,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>OTOGL</t>
+          <t>PCNA</t>
         </is>
       </c>
       <c r="B250" t="b">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Excit.L4_IT</t>
+          <t>Proliferation</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT</t>
+          <t>Base probe - Proliferation</t>
         </is>
       </c>
       <c r="G250" t="b">
@@ -8113,28 +8113,28 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>P2RY12</t>
+          <t>PCSK1</t>
         </is>
       </c>
       <c r="B251" t="b">
         <v>1</v>
       </c>
       <c r="C251">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Macro, Micro</t>
+          <t>Excit.L5_ET</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Base probe - Micro, DEG carrier included: Macro down</t>
+          <t>Base probe - Excit.L5_ET</t>
         </is>
       </c>
       <c r="G251" t="b">
@@ -8144,28 +8144,28 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>P2RY13</t>
+          <t>PCSK6</t>
         </is>
       </c>
       <c r="B252" t="b">
         <v>1</v>
       </c>
       <c r="C252">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, DEG - mediation</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Oligo, Oligo.3</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Oligo, DEG carrier included: Oligo.3 down, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G252" t="b">
@@ -8175,28 +8175,28 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PABPN1</t>
+          <t>PDGFD</t>
         </is>
       </c>
       <c r="B253" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C253">
         <v>2</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Astro.3, Excit.L2_5.1</t>
+          <t>Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Astro.3 specific MR genes - Astro.3/Astro.1: 1.046, Excit.L2_5.1 specific Enrich genes t= 9.16</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6, globl MR genes -  Inhib.Lamp5_Lhx6/Excit.L2: 4.15</t>
         </is>
       </c>
       <c r="G253" t="b">
@@ -8206,7 +8206,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PAX6</t>
+          <t>PDGFRA</t>
         </is>
       </c>
       <c r="B254" t="b">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="G254" t="b">
@@ -8237,28 +8237,28 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>PCDH9-AS2</t>
+          <t>PECAM1</t>
         </is>
       </c>
       <c r="B255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C255">
         <v>1</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Astro.1 specific MR genes - Astro.1/Astro.3: 1.486</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="G255" t="b">
@@ -8268,7 +8268,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PCNA</t>
+          <t>PHLDB2</t>
         </is>
       </c>
       <c r="B256" t="b">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Proliferation</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Base probe - Proliferation</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="G256" t="b">
@@ -8299,28 +8299,28 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PCSK1</t>
+          <t>PLCE1</t>
         </is>
       </c>
       <c r="B257" t="b">
         <v>1</v>
       </c>
       <c r="C257">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Excit.L5_ET</t>
+          <t>Astro.2, Astro.4, Excit.L6b, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_ET</t>
+          <t>Base probe - Vasc.VLMC, Astro.4 specific MR gene - Astro.4/Astro.5: 3.668, Excit.L6b specific MR gene - Excit.L6b/Excit.L2_5.1: 4.023, DEG carrier included: Astro.2 down</t>
         </is>
       </c>
       <c r="G257" t="b">
@@ -8330,28 +8330,28 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>PCSK6</t>
+          <t>PLCH1</t>
         </is>
       </c>
       <c r="B258" t="b">
         <v>1</v>
       </c>
       <c r="C258">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Oligo, Oligo.3</t>
+          <t>Excit.L2_5.2, Inhib.Sst</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, DEG carrier included: Oligo.3 down, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Inhib.Sst, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5.1: 1.52</t>
         </is>
       </c>
       <c r="G258" t="b">
@@ -8361,28 +8361,28 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>PDGFD</t>
+          <t>PLD5</t>
         </is>
       </c>
       <c r="B259" t="b">
         <v>1</v>
       </c>
       <c r="C259">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6, globl MR genes -  Inhib.Lamp5_Lhx6/Excit.L2: 4.15</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="G259" t="b">
@@ -8392,28 +8392,28 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PDGFRA</t>
+          <t>PLP1</t>
         </is>
       </c>
       <c r="B260" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C260">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Excit.L2_5.1, Oligo.3</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>Excit.L2_5.1 specific Enrich genes t= 8.05, DEG of interest: Oligo.3 down logFC=-0.93</t>
         </is>
       </c>
       <c r="G260" t="b">
@@ -8423,28 +8423,28 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>PECAM1</t>
+          <t>PLPPR4</t>
         </is>
       </c>
       <c r="B261" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>mediation gene: mediator Astro.1</t>
         </is>
       </c>
       <c r="G261" t="b">
@@ -8454,7 +8454,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PHLDB2</t>
+          <t>POSTN</t>
         </is>
       </c>
       <c r="B262" t="b">
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G262" t="b">
@@ -8485,28 +8485,28 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PLCE1</t>
+          <t>POU6F2</t>
         </is>
       </c>
       <c r="B263" t="b">
         <v>1</v>
       </c>
       <c r="C263">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Astro.2, Astro.4, Excit.L6b, Vasc.VLMC</t>
+          <t>Excit.L4_IT</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC, Astro.4 specific MR gene - Astro.4/Astro.5: 3.668, Excit.L6b specific MR gene - Excit.L6b/Excit.L2_5.1: 4.023, DEG carrier included: Astro.2 down</t>
+          <t>Base probe - Excit.L4_IT</t>
         </is>
       </c>
       <c r="G263" t="b">
@@ -8516,7 +8516,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PLCH1</t>
+          <t>PROX1</t>
         </is>
       </c>
       <c r="B264" t="b">
@@ -8527,17 +8527,17 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2, Inhib.Sst</t>
+          <t>Inhib.Sncg, Inhib.Vip</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5.1: 1.52</t>
+          <t>Base probe - Inhib.Sncg, globl MR genes -  Inhib.Vip/Oligo.2: 1.345</t>
         </is>
       </c>
       <c r="G264" t="b">
@@ -8547,28 +8547,28 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PLD5</t>
+          <t>PSEN1</t>
         </is>
       </c>
       <c r="B265" t="b">
         <v>1</v>
       </c>
       <c r="C265">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, Lit - AD risk</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Oligo, Oligo.3</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>Base probe - Oligo, OpenTargets AD gene, DEG carrier included: Oligo.3 down</t>
         </is>
       </c>
       <c r="G265" t="b">
@@ -8578,28 +8578,28 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PLP1</t>
+          <t>PSEN2</t>
         </is>
       </c>
       <c r="B266" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C266">
         <v>2</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>DEG - carrier, Marker - cell type specific</t>
+          <t>Base, Lit - AD risk</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1, Oligo.3</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1 specific Enrich genes t= 8.05, DEG of interest: Oligo.3 down</t>
+          <t>Base probe - Glioblastoma_cancer, OpenTargets AD gene</t>
         </is>
       </c>
       <c r="G266" t="b">
@@ -8609,28 +8609,28 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PLPPR4</t>
+          <t>PSENEN</t>
         </is>
       </c>
       <c r="B267" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C267">
         <v>1</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.1</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G267" t="b">
@@ -8640,7 +8640,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>POSTN</t>
+          <t>PTCHD4</t>
         </is>
       </c>
       <c r="B268" t="b">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Inhib.Lamp5</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Inhib.Lamp5</t>
         </is>
       </c>
       <c r="G268" t="b">
@@ -8671,28 +8671,28 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>POU6F2</t>
+          <t>PTGDS</t>
         </is>
       </c>
       <c r="B269" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C269">
         <v>1</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Excit.L4_IT</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT</t>
+          <t>Astro.2 specific MR genes - Astro.2/Astro.5: 1.01, Astro.2 specific Enrich genes t= 4.92</t>
         </is>
       </c>
       <c r="G269" t="b">
@@ -8702,28 +8702,28 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>PRKD1</t>
+          <t>PTPRC</t>
         </is>
       </c>
       <c r="B270" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C270">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base, DEG - ancestry, DEG - carrier</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Micro, Oligo.3, Oligo.5</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L5.2 down</t>
+          <t>Base probe - Micro, DEG carrier included: Oligo.3 up, DEG carrier top: Oligo.3 up logFC=3.24, DEG carrier included: Oligo.5 up, DEG carrier top: Oligo.3 AA_up</t>
         </is>
       </c>
       <c r="G270" t="b">
@@ -8733,28 +8733,28 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PROX1</t>
+          <t>PTPRD</t>
         </is>
       </c>
       <c r="B271" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C271">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Inhib.Sncg, Inhib.Vip</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sncg, globl MR genes -  Inhib.Vip/Oligo.2: 1.345</t>
+          <t>DEG LR interactions: IL1RAPL1 -&gt; PTPRD,NTRK3 -&gt; PTPRD</t>
         </is>
       </c>
       <c r="G271" t="b">
@@ -8764,28 +8764,28 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>PSEN1</t>
+          <t>PTPRZ1</t>
         </is>
       </c>
       <c r="B272" t="b">
         <v>1</v>
       </c>
       <c r="C272">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Lit - AD risk</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Oligo, Oligo.3</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, OpenTargets AD gene, DEG carrier included: Oligo.3 down</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="G272" t="b">
@@ -8795,28 +8795,28 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>PSEN2</t>
+          <t>PVALB</t>
         </is>
       </c>
       <c r="B273" t="b">
         <v>1</v>
       </c>
       <c r="C273">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Base, Lit - AD risk</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, OpenTargets AD gene</t>
+          <t>Base probe - Inhib.Chandelier</t>
         </is>
       </c>
       <c r="G273" t="b">
@@ -8826,28 +8826,28 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>PSENEN</t>
+          <t>RABL2B</t>
         </is>
       </c>
       <c r="B274" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
         </is>
       </c>
       <c r="G274" t="b">
@@ -8857,7 +8857,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>PTCHD4</t>
+          <t>RASGRP1</t>
         </is>
       </c>
       <c r="B275" t="b">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G275" t="b">
@@ -8888,28 +8888,28 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>PTGDS</t>
+          <t>RELN</t>
         </is>
       </c>
       <c r="B276" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C276">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, Marker - SpD</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Inhib.Pax6, L2.3~Sp09D01</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Astro.2 specific MR genes - Astro.2/Astro.5: 1.01, Astro.2 specific Enrich genes t= 4.92</t>
+          <t>Base probe - Inhib.Pax6, SpD marker from Lit</t>
         </is>
       </c>
       <c r="G276" t="b">
@@ -8919,28 +8919,28 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>PTPRC</t>
+          <t>RFTN1</t>
         </is>
       </c>
       <c r="B277" t="b">
         <v>1</v>
       </c>
       <c r="C277">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Base, DEG - ancestry, DEG - carrier</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Micro, Oligo.3, Oligo.5</t>
+          <t>Oligo.3, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Base probe - Micro, DEG carrier included: Oligo.3 up, DEG carrier top: Oligo.3 up, DEG carrier included: Oligo.5 up, DEG carrier top: Oligo.3 AA_up</t>
+          <t>Base probe - Vasc.VLMC, DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="G277" t="b">
@@ -8950,28 +8950,28 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>PTPRD</t>
+          <t>RGS10</t>
         </is>
       </c>
       <c r="B278" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C278">
         <v>1</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>DEG LR interactions: IL1RAPL1 -&gt; PTPRD,NTRK3 -&gt; PTPRD</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G278" t="b">
@@ -8981,7 +8981,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>PTPRZ1</t>
+          <t>RGS16</t>
         </is>
       </c>
       <c r="B279" t="b">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G279" t="b">
@@ -9012,28 +9012,28 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>PVALB</t>
+          <t>RIT2</t>
         </is>
       </c>
       <c r="B280" t="b">
         <v>1</v>
       </c>
       <c r="C280">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Inhib.Chandelier</t>
+          <t>Excit.L2_5.2, Excit.L5_ET</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier</t>
+          <t>Base probe - Excit.L5_ET, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L6_CT: 2.087</t>
         </is>
       </c>
       <c r="G280" t="b">
@@ -9043,7 +9043,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>RABL2B</t>
+          <t>RNASE1</t>
         </is>
       </c>
       <c r="B281" t="b">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>MOFA - Factor3</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
+          <t>MOFA Oligo.3 Factor3-</t>
         </is>
       </c>
       <c r="G281" t="b">
@@ -9074,28 +9074,28 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>RASGRP1</t>
+          <t>RNASET2</t>
         </is>
       </c>
       <c r="B282" t="b">
         <v>1</v>
       </c>
       <c r="C282">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Glioblastoma_TME, Oligo.3</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Glioblastoma_TME, DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="G282" t="b">
@@ -9105,28 +9105,28 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>RELN</t>
+          <t>RNF144B</t>
         </is>
       </c>
       <c r="B283" t="b">
         <v>1</v>
       </c>
       <c r="C283">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Base, Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Inhib.Pax6, L2.3~Sp09D01</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6, SpD marker from Lit</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="G283" t="b">
@@ -9136,7 +9136,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>RFTN1</t>
+          <t>RORB</t>
         </is>
       </c>
       <c r="B284" t="b">
@@ -9147,17 +9147,17 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Oligo.3, Vasc.VLMC</t>
+          <t>Excit.L4_IT, Excit.L5.1</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC, DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Excit.L4_IT, Excit.L5.1 specific MR gene - Excit.L5.1/Excit.L2_5.1: 4.221</t>
         </is>
       </c>
       <c r="G284" t="b">
@@ -9167,28 +9167,28 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>RGS10</t>
+          <t>ROS1</t>
         </is>
       </c>
       <c r="B285" t="b">
         <v>1</v>
       </c>
       <c r="C285">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type global, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Excit.L6b</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Excit.L6b, globl MR genes -  Excit.L6b/Excit.L2: 5.636, Excit.L6b specific MR gene - Excit.L6b/Excit.L2: 5.636</t>
         </is>
       </c>
       <c r="G285" t="b">
@@ -9198,28 +9198,28 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>RGS16</t>
+          <t>RPS27</t>
         </is>
       </c>
       <c r="B286" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C286">
         <v>1</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Astro.3 specific MR genes - Astro.3/Astro.2: 1.109</t>
         </is>
       </c>
       <c r="G286" t="b">
@@ -9229,7 +9229,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>RIT2</t>
+          <t>RSPO2</t>
         </is>
       </c>
       <c r="B287" t="b">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2, Excit.L5_ET</t>
+          <t>Excit.L5.2, Inhib.Pvalb</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_ET, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L6_CT: 2.087</t>
+          <t>Base probe - Inhib.Pvalb, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2: 1.829</t>
         </is>
       </c>
       <c r="G287" t="b">
@@ -9260,28 +9260,28 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>RNASET2</t>
+          <t>RXFP1</t>
         </is>
       </c>
       <c r="B288" t="b">
         <v>1</v>
       </c>
       <c r="C288">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME, Oligo.3</t>
+          <t>Excit.L5_IT</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME, DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Excit.L5_IT</t>
         </is>
       </c>
       <c r="G288" t="b">
@@ -9291,7 +9291,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>RNF144B</t>
+          <t>RYR3</t>
         </is>
       </c>
       <c r="B289" t="b">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="G289" t="b">
@@ -9322,28 +9322,28 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>RORB</t>
+          <t>S100A4</t>
         </is>
       </c>
       <c r="B290" t="b">
         <v>1</v>
       </c>
       <c r="C290">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Excit.L4_IT, Excit.L5.1</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT, Excit.L5.1 specific MR gene - Excit.L5.1/Excit.L2_5.1: 4.221</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G290" t="b">
@@ -9353,28 +9353,28 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ROS1</t>
+          <t>SAMD5</t>
         </is>
       </c>
       <c r="B291" t="b">
         <v>1</v>
       </c>
       <c r="C291">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Excit.L6b</t>
+          <t>Inhib.Pvalb</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6b, globl MR genes -  Excit.L6b/Excit.L2: 5.636, Excit.L6b specific MR gene - Excit.L6b/Excit.L2: 5.636</t>
+          <t>Base probe - Inhib.Pvalb</t>
         </is>
       </c>
       <c r="G291" t="b">
@@ -9384,28 +9384,28 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>RPS27</t>
+          <t>SDK1</t>
         </is>
       </c>
       <c r="B292" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C292">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Excit.L5_6_NP, Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Astro.3 specific MR genes - Astro.3/Astro.2: 1.109</t>
+          <t>Base probe - Inhib.Chandelier, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 1.88</t>
         </is>
       </c>
       <c r="G292" t="b">
@@ -9415,28 +9415,28 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>RSPO2</t>
+          <t>SELENOP</t>
         </is>
       </c>
       <c r="B293" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C293">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>MOFA - Factor3</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Excit.L5.2, Inhib.Pvalb</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2: 1.829</t>
+          <t>MOFA Oligo.3 Factor3-</t>
         </is>
       </c>
       <c r="G293" t="b">
@@ -9446,7 +9446,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>RXFP1</t>
+          <t>SEMA5A</t>
         </is>
       </c>
       <c r="B294" t="b">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Excit.L5_IT</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_IT</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="G294" t="b">
@@ -9477,28 +9477,28 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>RYR3</t>
+          <t>SEMA6D</t>
         </is>
       </c>
       <c r="B295" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Oligo.1</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.2: 1.179</t>
         </is>
       </c>
       <c r="G295" t="b">
@@ -9508,7 +9508,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>S100A4</t>
+          <t>SERPINA3</t>
         </is>
       </c>
       <c r="B296" t="b">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="G296" t="b">
@@ -9539,7 +9539,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>SAMD5</t>
+          <t>SFRP2</t>
         </is>
       </c>
       <c r="B297" t="b">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="G297" t="b">
@@ -9570,28 +9570,28 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>SDK1</t>
+          <t>SGSM3</t>
         </is>
       </c>
       <c r="B298" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C298">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, Inhib.Chandelier</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 1.88</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up*-EA_down</t>
         </is>
       </c>
       <c r="G298" t="b">
@@ -9601,28 +9601,28 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>SELENOP</t>
+          <t>SLC17A6</t>
         </is>
       </c>
       <c r="B299" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C299">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>MOFA - Factor3</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L4_IT, Excit.L5.2</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>MOFA Oligo.3 Factor3-</t>
+          <t>Base probe - Excit.L4_IT, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2: 1.542</t>
         </is>
       </c>
       <c r="G299" t="b">
@@ -9632,28 +9632,28 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>SEMA5A</t>
+          <t>SLC17A7</t>
         </is>
       </c>
       <c r="B300" t="b">
         <v>1</v>
       </c>
       <c r="C300">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, DEG - mediation</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Excit.L6b, Oligo.3</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>Base probe - Excit.L6b, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G300" t="b">
@@ -9663,7 +9663,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>SEMA6D</t>
+          <t>SLC24A2</t>
         </is>
       </c>
       <c r="B301" t="b">
@@ -9679,12 +9679,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Oligo.1</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.2: 1.179</t>
+          <t>Astro.3 specific Enrich genes t= 8.18</t>
         </is>
       </c>
       <c r="G301" t="b">
@@ -9694,28 +9694,28 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>SERPINA3</t>
+          <t>SLC24A3</t>
         </is>
       </c>
       <c r="B302" t="b">
         <v>1</v>
       </c>
       <c r="C302">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, DEG - mediation</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Inhib.Vip, Oligo.3</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Inhib.Vip, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G302" t="b">
@@ -9725,7 +9725,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>SFRP2</t>
+          <t>SLC26A4</t>
         </is>
       </c>
       <c r="B303" t="b">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G303" t="b">
@@ -9756,7 +9756,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>SGSM3</t>
+          <t>SLC4A4</t>
         </is>
       </c>
       <c r="B304" t="b">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>MOFA - Factor3</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up*-EA_down</t>
+          <t>MOFA Oligo.3 Factor3+</t>
         </is>
       </c>
       <c r="G304" t="b">
@@ -9787,28 +9787,28 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>SLC17A6</t>
+          <t>SLC5A11</t>
         </is>
       </c>
       <c r="B305" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C305">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Excit.L4_IT, Excit.L5.2</t>
+          <t>Oligo.2</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2: 1.542</t>
+          <t>globl MR genes -  Oligo.2/Oligo.5: 1.492</t>
         </is>
       </c>
       <c r="G305" t="b">
@@ -9818,28 +9818,28 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>SLC17A7</t>
+          <t>SLIT3</t>
         </is>
       </c>
       <c r="B306" t="b">
         <v>1</v>
       </c>
       <c r="C306">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Excit.L6b, Oligo.3</t>
+          <t>Excit.L5_ET</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6b, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Excit.L5_ET</t>
         </is>
       </c>
       <c r="G306" t="b">
@@ -9849,28 +9849,28 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>SLC24A2</t>
+          <t>SNCG</t>
         </is>
       </c>
       <c r="B307" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C307">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Excit.L5_ET, Excit.L5.2</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Astro.3 specific Enrich genes t= 8.18</t>
+          <t>Base probe - Excit.L5_ET, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.893</t>
         </is>
       </c>
       <c r="G307" t="b">
@@ -9880,28 +9880,28 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>SLC24A3</t>
+          <t>SNRNP70</t>
         </is>
       </c>
       <c r="B308" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C308">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Inhib.Vip, Oligo.3</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Vip, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Astro.2 specific MR genes - Astro.2/Astro.3: 1.023</t>
         </is>
       </c>
       <c r="G308" t="b">
@@ -9911,28 +9911,28 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>SLC26A4</t>
+          <t>SNTA1</t>
         </is>
       </c>
       <c r="B309" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C309">
         <v>1</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Astro.2 specific Enrich genes t= 4.98</t>
         </is>
       </c>
       <c r="G309" t="b">
@@ -9942,28 +9942,28 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SLC4A4</t>
+          <t>SNTB2</t>
         </is>
       </c>
       <c r="B310" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C310">
         <v>1</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>MOFA - Factor3</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6_IT</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>MOFA Oligo.3 Factor3+</t>
+          <t>Base probe - Excit.L6_IT</t>
         </is>
       </c>
       <c r="G310" t="b">
@@ -9973,7 +9973,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>SLC7A11</t>
+          <t>SNX19</t>
         </is>
       </c>
       <c r="B311" t="b">
@@ -9984,17 +9984,17 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L5.2 up</t>
+          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
         </is>
       </c>
       <c r="G311" t="b">
@@ -10004,28 +10004,28 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>SLIT3</t>
+          <t>SORBS1</t>
         </is>
       </c>
       <c r="B312" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C312">
         <v>1</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Excit.L5_ET</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_ET</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G312" t="b">
@@ -10035,28 +10035,28 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>SNCG</t>
+          <t>SORCS1</t>
         </is>
       </c>
       <c r="B313" t="b">
         <v>1</v>
       </c>
       <c r="C313">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base, DEG - carrier, DEG - mediation, Lit - AD risk</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Excit.L5_ET, Excit.L5.2</t>
+          <t>Excit.L5_ET, Oligo.3</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_ET, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.893</t>
+          <t>Base probe - Excit.L5_ET, OpenTargets AD gene, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G313" t="b">
@@ -10066,28 +10066,28 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>SNRNP70</t>
+          <t>SOX10</t>
         </is>
       </c>
       <c r="B314" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C314">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Oligo.3, OPC</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Astro.2 specific MR genes - Astro.2/Astro.3: 1.023</t>
+          <t>Base probe - OPC, DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.64</t>
         </is>
       </c>
       <c r="G314" t="b">
@@ -10097,28 +10097,28 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>SNTA1</t>
+          <t>SOX11</t>
         </is>
       </c>
       <c r="B315" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C315">
         <v>1</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Astro.2 specific Enrich genes t= 4.98</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G315" t="b">
@@ -10128,7 +10128,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>SNTB2</t>
+          <t>SOX2</t>
         </is>
       </c>
       <c r="B316" t="b">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Excit.L6_IT</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G316" t="b">
@@ -10159,28 +10159,28 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>SNX19</t>
+          <t>SOX4</t>
         </is>
       </c>
       <c r="B317" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C317">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L5_6_NP, Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
+          <t>Base probe - Glioblastoma_cancer, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L5.2: 1.763</t>
         </is>
       </c>
       <c r="G317" t="b">
@@ -10190,28 +10190,28 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>SORBS1</t>
+          <t>SOX9</t>
         </is>
       </c>
       <c r="B318" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C318">
         <v>1</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="G318" t="b">
@@ -10221,28 +10221,28 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>SORCS1</t>
+          <t>SPHKAP</t>
         </is>
       </c>
       <c r="B319" t="b">
         <v>1</v>
       </c>
       <c r="C319">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, Lit - AD risk</t>
+          <t>Base, DEG - carrier, DEG - mediation</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Excit.L5_ET, Oligo.3</t>
+          <t>Inhib.Lamp5_Lhx6, Oligo.3</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_ET, OpenTargets AD gene, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G319" t="b">
@@ -10252,28 +10252,28 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>SOX10</t>
+          <t>SPI1</t>
         </is>
       </c>
       <c r="B320" t="b">
         <v>1</v>
       </c>
       <c r="C320">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Oligo.3, OPC</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Base probe - OPC, DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G320" t="b">
@@ -10283,28 +10283,28 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>SOX11</t>
+          <t>SPON1</t>
         </is>
       </c>
       <c r="B321" t="b">
         <v>1</v>
       </c>
       <c r="C321">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Astro, Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Astro, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.1: 3.554</t>
         </is>
       </c>
       <c r="G321" t="b">
@@ -10314,28 +10314,28 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>SOX2</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="B322" t="b">
         <v>1</v>
       </c>
       <c r="C322">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Inhib.Sst, Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Inhib.Sst_Chold, globl MR genes -  Inhib.Sst/Inhib.Vip: 7.019</t>
         </is>
       </c>
       <c r="G322" t="b">
@@ -10345,28 +10345,28 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>SOX4</t>
+          <t>ST18</t>
         </is>
       </c>
       <c r="B323" t="b">
         <v>1</v>
       </c>
       <c r="C323">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, Glioblastoma_cancer</t>
+          <t>Astro.2, Astro.3, Inhib.Vip, Oligo</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L5.2: 1.763</t>
+          <t>Base probe - Oligo, Astro.3 specific Enrich genes t= 7.88, DEG carrier included: Astro.2 down, DEG carrier included: Inhib.Vip down, mediation gene: mediator Astro.2</t>
         </is>
       </c>
       <c r="G323" t="b">
@@ -10376,7 +10376,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>SOX6</t>
+          <t>STAT1</t>
         </is>
       </c>
       <c r="B324" t="b">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>DEG of interest: Oligo.3 up logFC=0.8</t>
         </is>
       </c>
       <c r="G324" t="b">
@@ -10407,7 +10407,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>SOX9</t>
+          <t>STAT3</t>
         </is>
       </c>
       <c r="B325" t="b">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="G325" t="b">
@@ -10438,28 +10438,28 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>SPHKAP</t>
+          <t>STAT4</t>
         </is>
       </c>
       <c r="B326" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C326">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6, Oligo.3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>DEG of interest: Oligo.3 up logFC=2.62</t>
         </is>
       </c>
       <c r="G326" t="b">
@@ -10469,7 +10469,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>SPI1</t>
+          <t>STK32B</t>
         </is>
       </c>
       <c r="B327" t="b">
@@ -10485,12 +10485,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="G327" t="b">
@@ -10500,28 +10500,28 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>SPON1</t>
+          <t>STXBP2</t>
         </is>
       </c>
       <c r="B328" t="b">
         <v>1</v>
       </c>
       <c r="C328">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Astro, Excit.L5_6_NP</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Base probe - Astro, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.1: 3.554</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G328" t="b">
@@ -10531,7 +10531,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>SULF1</t>
         </is>
       </c>
       <c r="B329" t="b">
@@ -10542,17 +10542,17 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Inhib.Sst, Inhib.Sst_Chold</t>
+          <t>Excit.L6_CT, Inhib.Pvalb</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold, globl MR genes -  Inhib.Sst/Inhib.Vip: 7.019</t>
+          <t>Base probe - Inhib.Pvalb, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L6b: 4.385</t>
         </is>
       </c>
       <c r="G329" t="b">
@@ -10562,28 +10562,28 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ST18</t>
+          <t>SV2B</t>
         </is>
       </c>
       <c r="B330" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C330">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Astro.2, Astro.3, Inhib.Vip, Oligo</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, Astro.3 specific Enrich genes t= 7.88, DEG carrier included: Astro.2 down, DEG carrier included: Inhib.Vip down, mediation gene: mediator Astro.2</t>
+          <t>mediation gene: mediator Astro.2</t>
         </is>
       </c>
       <c r="G330" t="b">
@@ -10593,28 +10593,28 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>STAT1</t>
+          <t>SYNPR</t>
         </is>
       </c>
       <c r="B331" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C331">
         <v>1</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Sst</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>DEG of interest: Oligo.3 up</t>
+          <t>Base probe - Inhib.Sst</t>
         </is>
       </c>
       <c r="G331" t="b">
@@ -10624,28 +10624,28 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>STAT3</t>
+          <t>TAC1</t>
         </is>
       </c>
       <c r="B332" t="b">
         <v>1</v>
       </c>
       <c r="C332">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>Inhib.Pvalb, Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>Base probe - Inhib.Sst_Chold, globl MR genes -  Inhib.Pvalb/Inhib.Sst: 2.127</t>
         </is>
       </c>
       <c r="G332" t="b">
@@ -10655,28 +10655,28 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>STAT4</t>
+          <t>TACR1</t>
         </is>
       </c>
       <c r="B333" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C333">
         <v>1</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>DEG of interest: Oligo.3 up</t>
+          <t>Base probe - Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="G333" t="b">
@@ -10686,28 +10686,28 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>STK32B</t>
+          <t>TANK</t>
         </is>
       </c>
       <c r="B334" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C334">
         <v>1</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>Excit.L5.2 specific Enrich genes t= 13.71</t>
         </is>
       </c>
       <c r="G334" t="b">
@@ -10717,7 +10717,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>STXBP2</t>
+          <t>TENM1</t>
         </is>
       </c>
       <c r="B335" t="b">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Inhib.Chandelier</t>
         </is>
       </c>
       <c r="G335" t="b">
@@ -10748,28 +10748,28 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>SULF1</t>
+          <t>TESPA1</t>
         </is>
       </c>
       <c r="B336" t="b">
         <v>1</v>
       </c>
       <c r="C336">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Excit.L6_CT, Inhib.Pvalb</t>
+          <t>Excit.L2, Excit.L2_3_IT, Oligo.3</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L6b: 4.385</t>
+          <t>Base probe - Excit.L2_3_IT, Excit.L2 specific MR gene - Excit.L2/Excit.L6b: 1.646, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G336" t="b">
@@ -10779,28 +10779,28 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>SV2B</t>
+          <t>TGFB1</t>
         </is>
       </c>
       <c r="B337" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C337">
         <v>1</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.2</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G337" t="b">
@@ -10810,7 +10810,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>SYNPR</t>
+          <t>TGFB2</t>
         </is>
       </c>
       <c r="B338" t="b">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Inhib.Sst</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="G338" t="b">
@@ -10841,7 +10841,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>TAC1</t>
+          <t>TGFBI</t>
         </is>
       </c>
       <c r="B339" t="b">
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb, Inhib.Sst_Chold</t>
+          <t>Excit.L2_5.2, Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold, globl MR genes -  Inhib.Pvalb/Inhib.Sst: 2.127</t>
+          <t>Base probe - Glioblastoma_TME, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L2_5.1: 12.753, Excit.L2_5.2 specific Enrich genes t= 11.97</t>
         </is>
       </c>
       <c r="G339" t="b">
@@ -10872,28 +10872,28 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>TACR1</t>
+          <t>THBS1</t>
         </is>
       </c>
       <c r="B340" t="b">
         <v>1</v>
       </c>
       <c r="C340">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, DEG - mediation</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Inhib.Sst_Chold</t>
+          <t>Astro, Oligo.3</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold</t>
+          <t>Base probe - Astro, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G340" t="b">
@@ -10903,28 +10903,28 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>TANK</t>
+          <t>THEMIS</t>
         </is>
       </c>
       <c r="B341" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C341">
         <v>1</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Excit.L5.2 specific Enrich genes t= 13.71</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G341" t="b">
@@ -10934,28 +10934,28 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>TENM1</t>
+          <t>THSD4</t>
         </is>
       </c>
       <c r="B342" t="b">
         <v>1</v>
       </c>
       <c r="C342">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Inhib.Chandelier</t>
+          <t>Excit.L2_5.2, Oligo.3, Vasc.Endo</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier</t>
+          <t>Base probe - Vasc.Endo, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L2: 1.924, DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="G342" t="b">
@@ -10965,28 +10965,28 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>TESPA1</t>
+          <t>THSD7B</t>
         </is>
       </c>
       <c r="B343" t="b">
         <v>1</v>
       </c>
       <c r="C343">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Excit.L2, Excit.L2_3_IT, Oligo.3</t>
+          <t>Inhib.Sncg</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L2_3_IT, Excit.L2 specific MR gene - Excit.L2/Excit.L6b: 1.646, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Inhib.Sncg</t>
         </is>
       </c>
       <c r="G343" t="b">
@@ -10996,28 +10996,28 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>TGFB1</t>
+          <t>TLR2</t>
         </is>
       </c>
       <c r="B344" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C344">
         <v>1</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>DEG of interest: Oligo.3 up logFC=1.56</t>
         </is>
       </c>
       <c r="G344" t="b">
@@ -11027,28 +11027,28 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>TGFB2</t>
+          <t>TMEM132C</t>
         </is>
       </c>
       <c r="B345" t="b">
         <v>1</v>
       </c>
       <c r="C345">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Excit.L5_6_NP, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Base probe - Vasc.VLMC, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.1: 5.943</t>
         </is>
       </c>
       <c r="G345" t="b">
@@ -11058,28 +11058,28 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>TGFBI</t>
+          <t>TMIGD3</t>
         </is>
       </c>
       <c r="B346" t="b">
         <v>1</v>
       </c>
       <c r="C346">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2, Glioblastoma_TME</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L2_5.1: 12.753, Excit.L2_5.2 specific Enrich genes t= 11.97</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G346" t="b">
@@ -11089,28 +11089,28 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>THBS1</t>
+          <t>TNK2</t>
         </is>
       </c>
       <c r="B347" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C347">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Astro, Oligo.3</t>
+          <t>OPC.5</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Base probe - Astro, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>OPC.5 specific MR genes - OPC.5/OPC.2: 1.04</t>
         </is>
       </c>
       <c r="G347" t="b">
@@ -11120,7 +11120,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>THEMIS</t>
+          <t>TOP2A</t>
         </is>
       </c>
       <c r="B348" t="b">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Proliferation</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Proliferation</t>
         </is>
       </c>
       <c r="G348" t="b">
@@ -11151,28 +11151,28 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>THSD4</t>
+          <t>TP53</t>
         </is>
       </c>
       <c r="B349" t="b">
         <v>1</v>
       </c>
       <c r="C349">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2, Oligo.3, Vasc.Endo</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L2: 1.924, DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G349" t="b">
@@ -11182,7 +11182,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>THSD7B</t>
+          <t>TPH2</t>
         </is>
       </c>
       <c r="B350" t="b">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Inhib.Sncg</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sncg</t>
+          <t>Base probe - Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="G350" t="b">
@@ -11213,28 +11213,28 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>TLR2</t>
+          <t>TRAC</t>
         </is>
       </c>
       <c r="B351" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C351">
         <v>1</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>DEG of interest: Oligo.3 up</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G351" t="b">
@@ -11244,28 +11244,28 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>TMEM132C</t>
+          <t>TREM2</t>
         </is>
       </c>
       <c r="B352" t="b">
         <v>1</v>
       </c>
       <c r="C352">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, Vasc.VLMC</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.1: 5.943</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G352" t="b">
@@ -11275,28 +11275,28 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>TMIGD3</t>
+          <t>TRHDE</t>
         </is>
       </c>
       <c r="B353" t="b">
         <v>1</v>
       </c>
       <c r="C353">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Excit.L5_6_NP, Inhib.Sst</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Inhib.Sst, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.2: 1.521</t>
         </is>
       </c>
       <c r="G353" t="b">
@@ -11306,28 +11306,28 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>TNK2</t>
+          <t>TRIL</t>
         </is>
       </c>
       <c r="B354" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C354">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>OPC.5</t>
+          <t>Astro.2, Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>OPC.5 specific MR genes - OPC.5/OPC.2: 1.04</t>
+          <t>Base probe - Glioblastoma_cancer, DEG carrier included: Astro.2 up</t>
         </is>
       </c>
       <c r="G354" t="b">
@@ -11337,28 +11337,28 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>TOP2A</t>
+          <t>TRIM51</t>
         </is>
       </c>
       <c r="B355" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C355">
         <v>1</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Proliferation</t>
+          <t>WM.uf_Sp09D07-WM_Sp09D06</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Base probe - Proliferation</t>
+          <t>SpD pw gene t=7.53</t>
         </is>
       </c>
       <c r="G355" t="b">
@@ -11368,7 +11368,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>TP53</t>
+          <t>TRPC5</t>
         </is>
       </c>
       <c r="B356" t="b">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G356" t="b">
@@ -11399,7 +11399,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>TPH2</t>
+          <t>TRPC6</t>
         </is>
       </c>
       <c r="B357" t="b">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_6_NP</t>
+          <t>Base probe - Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="G357" t="b">
@@ -11430,28 +11430,28 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>TRAC</t>
+          <t>TSHZ2</t>
         </is>
       </c>
       <c r="B358" t="b">
         <v>1</v>
       </c>
       <c r="C358">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Astro.4, Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Excit.L5_6_NP, Astro.4 specific MR gene - Astro.4/Astro.5: 4.669, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L5.1: 1.691</t>
         </is>
       </c>
       <c r="G358" t="b">
@@ -11461,28 +11461,28 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>TREM2</t>
+          <t>TTYH1</t>
         </is>
       </c>
       <c r="B359" t="b">
         <v>1</v>
       </c>
       <c r="C359">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - SpD</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Glioblastoma_cancer, L1~Sp09D05</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Glioblastoma_cancer, SpD Enrich gene t=13.38</t>
         </is>
       </c>
       <c r="G359" t="b">
@@ -11492,28 +11492,28 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>TRHDE</t>
+          <t>UBXN2A</t>
         </is>
       </c>
       <c r="B360" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C360">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, Inhib.Sst</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.2: 1.521</t>
+          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
         </is>
       </c>
       <c r="G360" t="b">
@@ -11523,28 +11523,28 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>TRIL</t>
+          <t>UGT8</t>
         </is>
       </c>
       <c r="B361" t="b">
         <v>1</v>
       </c>
       <c r="C361">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base, DEG - carrier, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Astro.2, Glioblastoma_cancer</t>
+          <t>Astro.3, Oligo, Oligo.3</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, DEG carrier included: Astro.2 up</t>
+          <t>Base probe - Oligo, Astro.3 specific Enrich genes t= 7.67, DEG carrier included: Astro.3 down, DEG carrier included: Oligo.3 down</t>
         </is>
       </c>
       <c r="G361" t="b">
@@ -11554,7 +11554,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>TRPC5</t>
+          <t>UNC5B</t>
         </is>
       </c>
       <c r="B362" t="b">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Inhib.Chandelier</t>
         </is>
       </c>
       <c r="G362" t="b">
@@ -11585,28 +11585,28 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>TRPC6</t>
+          <t>VCAN</t>
         </is>
       </c>
       <c r="B363" t="b">
         <v>1</v>
       </c>
       <c r="C363">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Inhib.Sst_Chold</t>
+          <t>Astro.4, OPC</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold</t>
+          <t>Base probe - OPC, Astro.4 specific MR gene - Astro.4/Astro.5: 3.185</t>
         </is>
       </c>
       <c r="G363" t="b">
@@ -11616,28 +11616,28 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>TSHZ2</t>
+          <t>VIP</t>
         </is>
       </c>
       <c r="B364" t="b">
         <v>1</v>
       </c>
       <c r="C364">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Astro.4, Excit.L5_6_NP</t>
+          <t>Inhib.Vip</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_6_NP, Astro.4 specific MR gene - Astro.4/Astro.5: 4.669, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L5.1: 1.691</t>
+          <t>Base probe - Inhib.Vip</t>
         </is>
       </c>
       <c r="G364" t="b">
@@ -11647,28 +11647,28 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>TTYH1</t>
+          <t>VPS54</t>
         </is>
       </c>
       <c r="B365" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C365">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Base, Marker - SpD</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer, L1~Sp09D05</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, SpD Enrich gene t=13.38</t>
+          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
         </is>
       </c>
       <c r="G365" t="b">
@@ -11678,28 +11678,28 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>UBXN2A</t>
+          <t>VWC2L</t>
         </is>
       </c>
       <c r="B366" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C366">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L2_5.2, Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
+          <t>Base probe - Excit.L5_6_NP, DEG carrier included: Excit.L2_5.2 up</t>
         </is>
       </c>
       <c r="G366" t="b">
@@ -11709,28 +11709,28 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>UGT8</t>
+          <t>WIF1</t>
         </is>
       </c>
       <c r="B367" t="b">
         <v>1</v>
       </c>
       <c r="C367">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type specific</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Astro.3, Oligo, Oligo.3</t>
+          <t>Excit.L5.2, Inhib.Pax6</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, Astro.3 specific Enrich genes t= 7.67, DEG carrier included: Astro.3 down, DEG carrier included: Oligo.3 down</t>
+          <t>Base probe - Inhib.Pax6, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.998</t>
         </is>
       </c>
       <c r="G367" t="b">
@@ -11740,7 +11740,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>UNC5B</t>
+          <t>ZBBX</t>
         </is>
       </c>
       <c r="B368" t="b">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Inhib.Chandelier</t>
+          <t>Excit.L2_3_IT</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier</t>
+          <t>Base probe - Excit.L2_3_IT</t>
         </is>
       </c>
       <c r="G368" t="b">
@@ -11771,28 +11771,28 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>VCAN</t>
+          <t>ZDHHC11</t>
         </is>
       </c>
       <c r="B369" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C369">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Astro.4, OPC</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Base probe - OPC, Astro.4 specific MR gene - Astro.4/Astro.5: 3.185</t>
+          <t>DEG carrier top:  Excit.L5.2 down</t>
         </is>
       </c>
       <c r="G369" t="b">
@@ -11802,7 +11802,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>ZDHHC23</t>
         </is>
       </c>
       <c r="B370" t="b">
@@ -11818,170 +11818,15 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Inhib.Vip</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Vip</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G370" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>VPS54</t>
-        </is>
-      </c>
-      <c r="B371" t="b">
-        <v>0</v>
-      </c>
-      <c r="C371">
-        <v>1</v>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>DEG - ancestry</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>Oligo.3</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
-        </is>
-      </c>
-      <c r="G371" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>VWC2L</t>
-        </is>
-      </c>
-      <c r="B372" t="b">
-        <v>1</v>
-      </c>
-      <c r="C372">
-        <v>2</v>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>Base, DEG - carrier</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>Excit.L2_5.2, Excit.L5_6_NP</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>Base probe - Excit.L5_6_NP, DEG carrier included: Excit.L2_5.2 up</t>
-        </is>
-      </c>
-      <c r="G372" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>WIF1</t>
-        </is>
-      </c>
-      <c r="B373" t="b">
-        <v>1</v>
-      </c>
-      <c r="C373">
-        <v>2</v>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>Base, Marker - cell type specific</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>Excit.L5.2, Inhib.Pax6</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>Base probe - Inhib.Pax6, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.998</t>
-        </is>
-      </c>
-      <c r="G373" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>ZBBX</t>
-        </is>
-      </c>
-      <c r="B374" t="b">
-        <v>1</v>
-      </c>
-      <c r="C374">
-        <v>1</v>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>Excit.L2_3_IT</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>Base probe - Excit.L2_3_IT</t>
-        </is>
-      </c>
-      <c r="G374" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>ZDHHC23</t>
-        </is>
-      </c>
-      <c r="B375" t="b">
-        <v>1</v>
-      </c>
-      <c r="C375">
-        <v>1</v>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>Excit.L6_IT_Car3</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
-        </is>
-      </c>
-      <c r="G375" t="b">
         <v>1</v>
       </c>
     </row>

--- a/processed-data/21_Xenium/02_xenium_compile_custom/ERC_Xenium_ALL_probes_summary.xlsx
+++ b/processed-data/21_Xenium/02_xenium_compile_custom/ERC_Xenium_ALL_probes_summary.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G370"/>
+  <dimension ref="A1:G367"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1052,11 +1052,11 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Marker - cell type global, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oligo.5 specific MR genes - Oligo.5/Oligo.2: 2.851, Oligo.5 specific Enrich genes t= 12.26</t>
+          <t>globl MR genes -  Oligo.5/Excit.L2_5.2: 1.322, Oligo.5 specific MR genes - Oligo.5/Oligo.2: 2.851, Oligo.5 specific Enrich genes t= 12.26</t>
         </is>
       </c>
       <c r="G23" t="b">
@@ -2347,28 +2347,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CHODL</t>
+          <t>CHN1</t>
         </is>
       </c>
       <c r="B65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65">
         <v>1</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>WM.uf_Sp09D07-WM_Sp09D06</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>SpD pw gene t=8.2</t>
         </is>
       </c>
       <c r="G65" t="b">
@@ -2378,28 +2378,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CHRM3</t>
+          <t>CHODL</t>
         </is>
       </c>
       <c r="B66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.3</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G66" t="b">
@@ -2409,7 +2409,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CHST11</t>
+          <t>CHRM3</t>
         </is>
       </c>
       <c r="B67" t="b">
@@ -2420,17 +2420,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 up logFC=2.82</t>
+          <t>mediation gene: mediator Astro.3</t>
         </is>
       </c>
       <c r="G67" t="b">
@@ -2440,28 +2440,28 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CLDN11</t>
+          <t>CHST11</t>
         </is>
       </c>
       <c r="B68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>DEG carrier top: Oligo.3 up logFC=2.82</t>
         </is>
       </c>
       <c r="G68" t="b">
@@ -2471,28 +2471,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CNDP1</t>
+          <t>CLDN11</t>
         </is>
       </c>
       <c r="B69" t="b">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Astro.3, Inhib.Vip, Oligo, Oligo.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, DEG carrier included: Astro.3 down, DEG carrier included: Oligo.3 down, DEG carrier included: Inhib.Vip down</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G69" t="b">
@@ -2502,28 +2502,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CNTN2</t>
+          <t>CNDP1</t>
         </is>
       </c>
       <c r="B70" t="b">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Astro.3, Inhib.Vip, Oligo, Oligo.3</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Base probe - Oligo, DEG carrier included: Astro.3 down, DEG carrier included: Oligo.3 down, DEG carrier included: Inhib.Vip down</t>
         </is>
       </c>
       <c r="G70" t="b">
@@ -2533,28 +2533,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CNTNAP2</t>
+          <t>CNTN2</t>
         </is>
       </c>
       <c r="B71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oligo.3 specific MR genes - Oligo.3/Oligo.2: 1.055</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G71" t="b">
@@ -2564,28 +2564,28 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CNTNAP3B</t>
+          <t>CNTNAP2</t>
         </is>
       </c>
       <c r="B72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2, Inhib.Chandelier</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L6_CT: 1.699</t>
+          <t>Oligo.3 specific MR genes - Oligo.3/Oligo.2: 1.055</t>
         </is>
       </c>
       <c r="G72" t="b">
@@ -2595,7 +2595,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>COL12A1</t>
+          <t>CNTNAP3B</t>
         </is>
       </c>
       <c r="B73" t="b">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, Vasc.VLMC</t>
+          <t>Excit.L2_5.2, Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.016</t>
+          <t>Base probe - Inhib.Chandelier, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L6_CT: 1.699</t>
         </is>
       </c>
       <c r="G73" t="b">
@@ -2626,28 +2626,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>COL16A1</t>
+          <t>COL12A1</t>
         </is>
       </c>
       <c r="B74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Excit.L5_6_NP, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Astro.3 specific MR genes - Astro.3/Astro.2: 1.061</t>
+          <t>Base probe - Vasc.VLMC, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.016</t>
         </is>
       </c>
       <c r="G74" t="b">
@@ -2657,7 +2657,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>COL21A1</t>
+          <t>COL16A1</t>
         </is>
       </c>
       <c r="B75" t="b">
@@ -2668,17 +2668,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 up logFC=2.79</t>
+          <t>Astro.3 specific MR genes - Astro.3/Astro.2: 1.061</t>
         </is>
       </c>
       <c r="G75" t="b">
@@ -2688,28 +2688,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>COL25A1</t>
+          <t>COL21A1</t>
         </is>
       </c>
       <c r="B76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Inhib.Sst</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst, globl MR genes -  Inhib.Sst/Inhib.Lamp5_Lhx6: 1.643</t>
+          <t>DEG carrier top: Oligo.3 up logFC=2.79</t>
         </is>
       </c>
       <c r="G76" t="b">
@@ -2719,28 +2719,28 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>COPS9</t>
+          <t>COL25A1</t>
         </is>
       </c>
       <c r="B77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LD~Sp09D02</t>
+          <t>Inhib.Sst</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SpD MeanRatio gene: LD~Sp09D02/Inhib~Sp09D09: 1.112</t>
+          <t>Base probe - Inhib.Sst, globl MR genes -  Inhib.Sst/Inhib.Lamp5_Lhx6: 1.643</t>
         </is>
       </c>
       <c r="G77" t="b">
@@ -2750,28 +2750,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CORO1A</t>
+          <t>COPS9</t>
         </is>
       </c>
       <c r="B78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>LD~Sp09D02</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>SpD MeanRatio gene: LD~Sp09D02/Inhib~Sp09D09: 1.112</t>
         </is>
       </c>
       <c r="G78" t="b">
@@ -2781,28 +2781,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CPNE4</t>
+          <t>CORO1A</t>
         </is>
       </c>
       <c r="B79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>DEG of interest: Oligo.3 up logFC=1.87</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G79" t="b">
@@ -2812,28 +2812,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CRHBP</t>
+          <t>CPNE4</t>
         </is>
       </c>
       <c r="B80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Inhib.Sst_Chold</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold</t>
+          <t>DEG of interest: Oligo.3 up logFC=1.87</t>
         </is>
       </c>
       <c r="G80" t="b">
@@ -2843,28 +2843,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CRYM</t>
+          <t>CRHBP</t>
         </is>
       </c>
       <c r="B81" t="b">
         <v>1</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_6_NP, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.121, Excit.L5_6_NP specific Enrich genes t= 11.41</t>
+          <t>Base probe - Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="G81" t="b">
@@ -2874,28 +2874,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CSPG4</t>
+          <t>CRYM</t>
         </is>
       </c>
       <c r="B82" t="b">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Excit.L5_6_NP, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.121, Excit.L5_6_NP specific Enrich genes t= 11.41</t>
         </is>
       </c>
       <c r="G82" t="b">
@@ -2905,28 +2905,28 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CTNNA3</t>
+          <t>CSPG4</t>
         </is>
       </c>
       <c r="B83" t="b">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Astro.3, Oligo</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, Astro.3 specific Enrich genes t= 7.63</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="G83" t="b">
@@ -2936,28 +2936,28 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>CTNNA3</t>
         </is>
       </c>
       <c r="B84" t="b">
         <v>1</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Astro.3, Oligo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Oligo, Astro.3 specific Enrich genes t= 7.63</t>
         </is>
       </c>
       <c r="G84" t="b">
@@ -2967,7 +2967,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CTSS</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B85" t="b">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G85" t="b">
@@ -2998,7 +2998,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CUX2</t>
+          <t>CTSS</t>
         </is>
       </c>
       <c r="B86" t="b">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Excit.L2_3_IT</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L2_3_IT</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G86" t="b">
@@ -3029,7 +3029,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CX3CR1</t>
+          <t>CUX2</t>
         </is>
       </c>
       <c r="B87" t="b">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Excit.L2_3_IT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Excit.L2_3_IT</t>
         </is>
       </c>
       <c r="G87" t="b">
@@ -3060,7 +3060,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CXCL14</t>
+          <t>CX3CR1</t>
         </is>
       </c>
       <c r="B88" t="b">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G88" t="b">
@@ -3091,7 +3091,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CXCR4</t>
+          <t>CXCL14</t>
         </is>
       </c>
       <c r="B89" t="b">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="G89" t="b">
@@ -3122,28 +3122,28 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CYTIP</t>
+          <t>CXCR4</t>
         </is>
       </c>
       <c r="B90" t="b">
         <v>1</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME, Oligo.5</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME, DEG carrier included: Oligo.5 up</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G90" t="b">
@@ -3153,28 +3153,28 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DCN</t>
+          <t>CYTIP</t>
         </is>
       </c>
       <c r="B91" t="b">
         <v>1</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Glioblastoma_TME, Oligo.5</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Glioblastoma_TME, DEG carrier included: Oligo.5 up</t>
         </is>
       </c>
       <c r="G91" t="b">
@@ -3184,7 +3184,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DDR2</t>
+          <t>DCN</t>
         </is>
       </c>
       <c r="B92" t="b">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="G92" t="b">
@@ -3215,28 +3215,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DNER</t>
+          <t>DDR2</t>
         </is>
       </c>
       <c r="B93" t="b">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific, Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Astro.4, Excit.L5.2, Inhib.Lamp5, Inhib~Sp09D09</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5, Astro.4 specific MR gene - Astro.4/Astro.1: 1.855, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.516, SpD MeanRatio gene: Inhib~Sp09D09/L5~Sp09D03: 1.798, SpD Enrich gene t=14.7</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="G93" t="b">
@@ -3246,28 +3246,28 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DVL2</t>
+          <t>DNER</t>
         </is>
       </c>
       <c r="B94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base, Marker - cell type specific, Marker - SpD</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Astro.4, Excit.L5.2, Inhib.Lamp5, Inhib~Sp09D09</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
+          <t>Base probe - Inhib.Lamp5, Astro.4 specific MR gene - Astro.4/Astro.1: 1.855, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.516, SpD MeanRatio gene: Inhib~Sp09D09/L5~Sp09D03: 1.798, SpD Enrich gene t=14.7</t>
         </is>
       </c>
       <c r="G94" t="b">
@@ -3277,28 +3277,28 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EFHD1</t>
+          <t>DVL2</t>
         </is>
       </c>
       <c r="B95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95">
         <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
         </is>
       </c>
       <c r="G95" t="b">
@@ -3308,7 +3308,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EGFR</t>
+          <t>EFHD1</t>
         </is>
       </c>
       <c r="B96" t="b">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G96" t="b">
@@ -3339,7 +3339,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ELOVL2</t>
+          <t>EGFR</t>
         </is>
       </c>
       <c r="B97" t="b">
@@ -3370,28 +3370,28 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ENC1</t>
+          <t>ELOVL2</t>
         </is>
       </c>
       <c r="B98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98">
         <v>1</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G98" t="b">
@@ -3401,7 +3401,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ENSG00000286293</t>
+          <t>ENC1</t>
         </is>
       </c>
       <c r="B99" t="b">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3422,48 +3422,48 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 EA_down</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ENSG00000286438</t>
+          <t>ERBB3</t>
         </is>
       </c>
       <c r="B100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base, DEG - carrier, DEG - mediation, DEGs - LR</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo, Oligo.3</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 EA_down</t>
+          <t>Base probe - Oligo, DEG carrier included: Oligo.3 down, mediation gene: outcome Oligo.3, DEG LR interactions: NRG3 -&gt; ERBB3</t>
         </is>
       </c>
       <c r="G100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ENSG00000289591</t>
+          <t>ERBB4</t>
         </is>
       </c>
       <c r="B101" t="b">
@@ -3474,48 +3474,48 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1</t>
+          <t>Oligo.1</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L2_5.1 down</t>
+          <t>Oligo.1 specific Enrich genes t= 5.58</t>
         </is>
       </c>
       <c r="G101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ERBB3</t>
+          <t>ERMN</t>
         </is>
       </c>
       <c r="B102" t="b">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, DEGs - LR</t>
+          <t>Base, DEG - carrier, DEG - mediation, Marker - SpD</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oligo, Oligo.3</t>
+          <t>Inhib.Vip, Oligo, Oligo.3, WM~Sp09D06</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, DEG carrier included: Oligo.3 down, mediation gene: outcome Oligo.3, DEG LR interactions: NRG3 -&gt; ERBB3</t>
+          <t>Base probe - Oligo, SpD MeanRatio gene: WM~Sp09D06/L6~Sp09D04: 4.59, DEG carrier included: Oligo.3 down, DEG carrier included: Inhib.Vip down, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G102" t="b">
@@ -3525,7 +3525,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ERBB4</t>
+          <t>EXOC7</t>
         </is>
       </c>
       <c r="B103" t="b">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oligo.1</t>
+          <t>OPC.5</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Oligo.1 specific Enrich genes t= 5.58</t>
+          <t>OPC.5 specific Enrich genes t= 7.33</t>
         </is>
       </c>
       <c r="G103" t="b">
@@ -3556,28 +3556,28 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ERMN</t>
+          <t>EYA4</t>
         </is>
       </c>
       <c r="B104" t="b">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, Marker - SpD</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Inhib.Vip, Oligo, Oligo.3, WM~Sp09D06</t>
+          <t>Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, SpD MeanRatio gene: WM~Sp09D06/L6~Sp09D04: 4.59, DEG carrier included: Oligo.3 down, DEG carrier included: Inhib.Vip down, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6, globl MR genes -  Inhib.Lamp5_Lhx6/Oligo.2: 6.508</t>
         </is>
       </c>
       <c r="G104" t="b">
@@ -3587,7 +3587,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EXOC7</t>
+          <t>FAM171B</t>
         </is>
       </c>
       <c r="B105" t="b">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OPC.5</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>OPC.5 specific Enrich genes t= 7.33</t>
+          <t>Astro.1 specific Enrich genes t= 8.3</t>
         </is>
       </c>
       <c r="G105" t="b">
@@ -3618,28 +3618,28 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EYA4</t>
+          <t>FASLG</t>
         </is>
       </c>
       <c r="B106" t="b">
         <v>1</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6, globl MR genes -  Inhib.Lamp5_Lhx6/Oligo.2: 6.508</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G106" t="b">
@@ -3649,28 +3649,28 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>FAM171B</t>
+          <t>FBLN1</t>
         </is>
       </c>
       <c r="B107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, DEG - ancestry</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Oligo.3, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Astro.1 specific Enrich genes t= 8.3</t>
+          <t>Base probe - Vasc.VLMC, DEG Ancestry op: Oligo.3 AA_down-EA_up*</t>
         </is>
       </c>
       <c r="G107" t="b">
@@ -3680,7 +3680,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FASLG</t>
+          <t>FCER1G</t>
         </is>
       </c>
       <c r="B108" t="b">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G108" t="b">
@@ -3711,28 +3711,28 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FBLN1</t>
+          <t>FCGR1A</t>
         </is>
       </c>
       <c r="B109" t="b">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Base, DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Oligo.3, Vasc.VLMC</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC, DEG Ancestry op: Oligo.3 AA_down-EA_up*</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G109" t="b">
@@ -3742,7 +3742,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FCER1G</t>
+          <t>FCGR3A</t>
         </is>
       </c>
       <c r="B110" t="b">
@@ -3773,7 +3773,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FCGR1A</t>
+          <t>FGFR2</t>
         </is>
       </c>
       <c r="B111" t="b">
@@ -3789,12 +3789,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G111" t="b">
@@ -3804,7 +3804,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FCGR3A</t>
+          <t>FGFR3</t>
         </is>
       </c>
       <c r="B112" t="b">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="G112" t="b">
@@ -3835,28 +3835,28 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FGFR2</t>
+          <t>FIGN</t>
         </is>
       </c>
       <c r="B113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C113">
         <v>1</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Oligo.1</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.4: 1.143</t>
         </is>
       </c>
       <c r="G113" t="b">
@@ -3866,7 +3866,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FGFR3</t>
+          <t>FILIP1</t>
         </is>
       </c>
       <c r="B114" t="b">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Excit.L6_CT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Base probe - Excit.L6_CT</t>
         </is>
       </c>
       <c r="G114" t="b">
@@ -3897,28 +3897,28 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FIGN</t>
+          <t>FLT1</t>
         </is>
       </c>
       <c r="B115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C115">
         <v>1</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Oligo.1</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.4: 1.143</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="G115" t="b">
@@ -3928,28 +3928,28 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>FILIP1</t>
+          <t>FOS</t>
         </is>
       </c>
       <c r="B116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C116">
         <v>1</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Excit.L6_CT</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_CT</t>
+          <t>DEG carrier top: Oligo.3 up logFC=2.77, DEG of interest: Oligo.3 up logFC=2.77</t>
         </is>
       </c>
       <c r="G116" t="b">
@@ -3959,7 +3959,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FLT1</t>
+          <t>FSTL4</t>
         </is>
       </c>
       <c r="B117" t="b">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>Excit.L4_IT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>Base probe - Excit.L4_IT</t>
         </is>
       </c>
       <c r="G117" t="b">
@@ -3990,7 +3990,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FOS</t>
+          <t>FZD8</t>
         </is>
       </c>
       <c r="B118" t="b">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 up logFC=2.77, DEG of interest: Oligo.3 up logFC=2.77</t>
+          <t>mediation gene: mediator Astro.2</t>
         </is>
       </c>
       <c r="G118" t="b">
@@ -4021,28 +4021,28 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FSTL4</t>
+          <t>GAD1</t>
         </is>
       </c>
       <c r="B119" t="b">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, DEG - mediation, Marker - SpD</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Excit.L4_IT</t>
+          <t>Inhib.Pvalb, Inhib~Sp09D09, Oligo.3</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT</t>
+          <t>Base probe - Inhib.Pvalb, SpD MeanRatio gene: Inhib~Sp09D09/LD~Sp09D02: 3.35, SpD Enrich gene t=17.85, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G119" t="b">
@@ -4052,28 +4052,28 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>FZD8</t>
+          <t>GAD2</t>
         </is>
       </c>
       <c r="B120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base, DEG - carrier, Marker - SpD</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Inhib.Lamp5_Lhx6, Inhib~Sp09D09, Oligo.3</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.2</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6, SpD MeanRatio gene: Inhib~Sp09D09/LD~Sp09D02: 3.308, SpD Enrich gene t=15.34, DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="G120" t="b">
@@ -4083,28 +4083,28 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>GAD1</t>
+          <t>GAS2L3</t>
         </is>
       </c>
       <c r="B121" t="b">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb, Inhib~Sp09D09, Oligo.3</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb, SpD MeanRatio gene: Inhib~Sp09D09/LD~Sp09D02: 3.35, SpD Enrich gene t=17.85, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G121" t="b">
@@ -4114,28 +4114,28 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>GAD2</t>
+          <t>GJA1</t>
         </is>
       </c>
       <c r="B122" t="b">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - SpD</t>
+          <t>Base, Marker - SpD</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6, Inhib~Sp09D09, Oligo.3</t>
+          <t>Astro, L1~Sp09D05</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6, SpD MeanRatio gene: Inhib~Sp09D09/LD~Sp09D02: 3.308, SpD Enrich gene t=15.34, DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Astro, SpD MeanRatio gene: L1~Sp09D05/LD~Sp09D02: 1.387</t>
         </is>
       </c>
       <c r="G122" t="b">
@@ -4145,28 +4145,28 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GAS2L3</t>
+          <t>GNA14-AS1</t>
         </is>
       </c>
       <c r="B123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C123">
         <v>1</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>globl MR genes -  Astro.1/Astro.3: 1.372</t>
         </is>
       </c>
       <c r="G123" t="b">
@@ -4176,28 +4176,28 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GJA1</t>
+          <t>GNLY</t>
         </is>
       </c>
       <c r="B124" t="b">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Base, Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Astro, L1~Sp09D05</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Base probe - Astro, SpD MeanRatio gene: L1~Sp09D05/LD~Sp09D02: 1.387</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G124" t="b">
@@ -4207,28 +4207,28 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GNLY</t>
+          <t>GOLGA7</t>
         </is>
       </c>
       <c r="B125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C125">
         <v>1</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.1</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Oligo.1 specific Enrich genes t= 5.54</t>
         </is>
       </c>
       <c r="G125" t="b">
@@ -4238,7 +4238,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GOLGA7</t>
+          <t>GOLGA8A</t>
         </is>
       </c>
       <c r="B126" t="b">
@@ -4249,17 +4249,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Oligo.1</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Oligo.1 specific Enrich genes t= 5.54</t>
+          <t>DEG carrier top: Excit.L5.2 up</t>
         </is>
       </c>
       <c r="G126" t="b">
@@ -4269,7 +4269,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GOLGA8A</t>
+          <t>GPC5-AS1</t>
         </is>
       </c>
       <c r="B127" t="b">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L5.2 up</t>
+          <t>Excit.L5.2 specific MR genes - Excit.L5.2/Excit.L5.1: 13.028</t>
         </is>
       </c>
       <c r="G127" t="b">
@@ -4300,7 +4300,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GPC5-AS1</t>
+          <t>GPC6</t>
         </is>
       </c>
       <c r="B128" t="b">
@@ -4311,17 +4311,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>MOFA - Factor3</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Excit.L5.2 specific MR genes - Excit.L5.2/Excit.L5.1: 13.028</t>
+          <t>MOFA Oligo.3 Factor3+</t>
         </is>
       </c>
       <c r="G128" t="b">
@@ -4331,18 +4331,18 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GPC6</t>
+          <t>GPM6A</t>
         </is>
       </c>
       <c r="B129" t="b">
         <v>0</v>
       </c>
       <c r="C129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>MOFA - Factor3</t>
+          <t>DEG - mediation, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>MOFA Oligo.3 Factor3+</t>
+          <t>Oligo.3 specific Enrich genes t= 9.66, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G129" t="b">
@@ -4362,28 +4362,28 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GPM6A</t>
+          <t>GPNMB</t>
         </is>
       </c>
       <c r="B130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DEG - mediation, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Oligo.3 specific Enrich genes t= 9.66, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G130" t="b">
@@ -4393,7 +4393,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GPNMB</t>
+          <t>GPR183</t>
         </is>
       </c>
       <c r="B131" t="b">
@@ -4424,7 +4424,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GPR183</t>
+          <t>GPR34</t>
         </is>
       </c>
       <c r="B132" t="b">
@@ -4455,7 +4455,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GPR34</t>
+          <t>GZMA</t>
         </is>
       </c>
       <c r="B133" t="b">
@@ -4486,28 +4486,28 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GZMA</t>
+          <t>HBB</t>
         </is>
       </c>
       <c r="B134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C134">
         <v>1</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>DEG carrier top: Oligo.3 AA_down</t>
         </is>
       </c>
       <c r="G134" t="b">
@@ -4517,28 +4517,28 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>HBB</t>
+          <t>HES1</t>
         </is>
       </c>
       <c r="B135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_cancer, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 AA_down</t>
+          <t>Base probe - Glioblastoma_cancer, DEG carrier included: Vasc.VLMC up</t>
         </is>
       </c>
       <c r="G135" t="b">
@@ -4548,28 +4548,28 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>HES1</t>
+          <t>HHATL</t>
         </is>
       </c>
       <c r="B136" t="b">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer, Vasc.VLMC</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, DEG carrier included: Vasc.VLMC up</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G136" t="b">
@@ -4579,7 +4579,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>HHATL</t>
+          <t>HILPDA</t>
         </is>
       </c>
       <c r="B137" t="b">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G137" t="b">
@@ -4610,7 +4610,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>HILPDA</t>
+          <t>HLA-DMB</t>
         </is>
       </c>
       <c r="B138" t="b">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G138" t="b">
@@ -4641,7 +4641,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>HLA-DMB</t>
+          <t>HLA-DQA1</t>
         </is>
       </c>
       <c r="B139" t="b">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G139" t="b">
@@ -4672,28 +4672,28 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>HLA-DQA1</t>
+          <t>HMCN2</t>
         </is>
       </c>
       <c r="B140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Excit.L5.2 specific MR genes - Excit.L5.2/Excit.L6b: 13.871</t>
         </is>
       </c>
       <c r="G140" t="b">
@@ -4703,7 +4703,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>HMCN2</t>
+          <t>HOTAIRM1</t>
         </is>
       </c>
       <c r="B141" t="b">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Excit.L5.2 specific MR genes - Excit.L5.2/Excit.L6b: 13.871</t>
+          <t>Excit.L5.2 specific Enrich genes t= 16.54</t>
         </is>
       </c>
       <c r="G141" t="b">
@@ -4734,28 +4734,28 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>HOTAIRM1</t>
+          <t>HS3ST2</t>
         </is>
       </c>
       <c r="B142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C142">
         <v>1</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Excit.L6_CT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Excit.L5.2 specific Enrich genes t= 16.54</t>
+          <t>Base probe - Excit.L6_CT</t>
         </is>
       </c>
       <c r="G142" t="b">
@@ -4765,7 +4765,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>HS3ST2</t>
+          <t>HS3ST4</t>
         </is>
       </c>
       <c r="B143" t="b">
@@ -4796,7 +4796,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>HS3ST4</t>
+          <t>HTR2A</t>
         </is>
       </c>
       <c r="B144" t="b">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Excit.L6_CT</t>
+          <t>Excit.L5_IT</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_CT</t>
+          <t>Base probe - Excit.L5_IT</t>
         </is>
       </c>
       <c r="G144" t="b">
@@ -4827,28 +4827,28 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>HTR2A</t>
+          <t>HTR2C</t>
         </is>
       </c>
       <c r="B145" t="b">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Excit.L5_IT</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_IT</t>
+          <t>Base probe - Excit.L5_6_NP, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.173</t>
         </is>
       </c>
       <c r="G145" t="b">
@@ -4858,28 +4858,28 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>HTR2C</t>
+          <t>IDH1</t>
         </is>
       </c>
       <c r="B146" t="b">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_6_NP, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.173</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G146" t="b">
@@ -4889,7 +4889,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>IDH1</t>
+          <t>IDH2</t>
         </is>
       </c>
       <c r="B147" t="b">
@@ -4920,7 +4920,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>IDH2</t>
+          <t>IDO1</t>
         </is>
       </c>
       <c r="B148" t="b">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G148" t="b">
@@ -4951,7 +4951,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>IDO1</t>
+          <t>IFITM3</t>
         </is>
       </c>
       <c r="B149" t="b">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G149" t="b">
@@ -4982,28 +4982,28 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>IFITM3</t>
+          <t>IGFBP3</t>
         </is>
       </c>
       <c r="B150" t="b">
         <v>1</v>
       </c>
       <c r="C150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Excit.L6b, Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Glioblastoma_cancer, Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 3.37</t>
         </is>
       </c>
       <c r="G150" t="b">
@@ -5013,28 +5013,28 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>IGFBP3</t>
+          <t>IGFBP4</t>
         </is>
       </c>
       <c r="B151" t="b">
         <v>1</v>
       </c>
       <c r="C151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Excit.L6b, Glioblastoma_cancer</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 3.37</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="G151" t="b">
@@ -5044,28 +5044,28 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>IGFBP4</t>
+          <t>IGFBP5</t>
         </is>
       </c>
       <c r="B152" t="b">
         <v>1</v>
       </c>
       <c r="C152">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Astro.2, Astro.4, Glioblastoma_cancer, Oligo.3</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Glioblastoma_cancer, Astro.4 specific MR gene - Astro.4/Astro.5: 4.236, DEG carrier included: Astro.2 down, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G152" t="b">
@@ -5075,28 +5075,28 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IGFBP5</t>
+          <t>IKZF1</t>
         </is>
       </c>
       <c r="B153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C153">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Astro.2, Astro.4, Glioblastoma_cancer, Oligo.3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, Astro.4 specific MR gene - Astro.4/Astro.5: 4.236, DEG carrier included: Astro.2 down, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>DEG carrier top: Oligo.3 up logFC=2.75</t>
         </is>
       </c>
       <c r="G153" t="b">
@@ -5106,7 +5106,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>IKZF1</t>
+          <t>IL6ST</t>
         </is>
       </c>
       <c r="B154" t="b">
@@ -5117,17 +5117,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 up logFC=2.75</t>
+          <t>mediation gene: mediator Astro.3</t>
         </is>
       </c>
       <c r="G154" t="b">
@@ -5137,28 +5137,28 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>IL6ST</t>
+          <t>IL7R</t>
         </is>
       </c>
       <c r="B155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C155">
         <v>1</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.3</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G155" t="b">
@@ -5168,28 +5168,28 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>IL7R</t>
+          <t>ITGA8</t>
         </is>
       </c>
       <c r="B156" t="b">
         <v>1</v>
       </c>
       <c r="C156">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Excit.L5_6_NP, OPC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - OPC, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6b: 3.576</t>
         </is>
       </c>
       <c r="G156" t="b">
@@ -5199,28 +5199,28 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ITGA8</t>
+          <t>ITGAM</t>
         </is>
       </c>
       <c r="B157" t="b">
         <v>1</v>
       </c>
       <c r="C157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, OPC</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Base probe - OPC, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6b: 3.576</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G157" t="b">
@@ -5230,28 +5230,28 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ITGAM</t>
+          <t>ITGAV</t>
         </is>
       </c>
       <c r="B158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C158">
         <v>1</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Oligo.2</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Oligo.2 specific MR genes - Oligo.2/Oligo.1: 1.663</t>
         </is>
       </c>
       <c r="G158" t="b">
@@ -5261,28 +5261,28 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ITGAV</t>
+          <t>ITGAX</t>
         </is>
       </c>
       <c r="B159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C159">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, DEG - carrier, Marker - cell type global</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Oligo.2</t>
+          <t>Micro, Micro.1, Oligo.3</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Oligo.2 specific MR genes - Oligo.2/Oligo.1: 1.663</t>
+          <t>Base probe - Micro, globl MR genes -  Micro.1/Micro.4: 1.044, DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="G159" t="b">
@@ -5292,28 +5292,28 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ITGAX</t>
+          <t>ITGB2</t>
         </is>
       </c>
       <c r="B160" t="b">
         <v>1</v>
       </c>
       <c r="C160">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Micro, Micro.1, Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Base probe - Micro, globl MR genes -  Micro.1/Micro.4: 1.044, DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G160" t="b">
@@ -5323,28 +5323,28 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ITGB2</t>
+          <t>KAT2A</t>
         </is>
       </c>
       <c r="B161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up*-EA_down</t>
         </is>
       </c>
       <c r="G161" t="b">
@@ -5354,7 +5354,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>KAT2A</t>
+          <t>KCND2</t>
         </is>
       </c>
       <c r="B162" t="b">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up*-EA_down</t>
+          <t>Oligo.3 specific Enrich genes t= 9.2</t>
         </is>
       </c>
       <c r="G162" t="b">
@@ -5385,28 +5385,28 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>KCND2</t>
+          <t>KCNH5</t>
         </is>
       </c>
       <c r="B163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C163">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6_CT</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Oligo.3 specific Enrich genes t= 9.2</t>
+          <t>Base probe - Excit.L6_CT, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L6b: 1.583</t>
         </is>
       </c>
       <c r="G163" t="b">
@@ -5416,28 +5416,28 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>KCNH5</t>
+          <t>KCNJ3</t>
         </is>
       </c>
       <c r="B164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Excit.L6_CT</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_CT, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L6b: 1.583</t>
+          <t>Oligo.3 specific Enrich genes t= 9.5</t>
         </is>
       </c>
       <c r="G164" t="b">
@@ -5447,28 +5447,28 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>KCNJ3</t>
+          <t>KIT</t>
         </is>
       </c>
       <c r="B165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C165">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, Marker - cell type global, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6_CT, Inhib.Lamp5_Lhx6, Proliferation</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Oligo.3 specific Enrich genes t= 9.5</t>
+          <t>Base probe - Proliferation, globl MR genes -  Inhib.Lamp5_Lhx6/Inhib.Vip: 3.628, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L5_6_NP: 7.823</t>
         </is>
       </c>
       <c r="G165" t="b">
@@ -5478,28 +5478,28 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>KIT</t>
+          <t>KLF2</t>
         </is>
       </c>
       <c r="B166" t="b">
         <v>1</v>
       </c>
       <c r="C166">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Excit.L6_CT, Inhib.Lamp5_Lhx6, Proliferation</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Base probe - Proliferation, globl MR genes -  Inhib.Lamp5_Lhx6/Inhib.Vip: 3.628, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L5_6_NP: 7.823</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G166" t="b">
@@ -5509,7 +5509,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>KLF2</t>
+          <t>KLF4</t>
         </is>
       </c>
       <c r="B167" t="b">
@@ -5540,7 +5540,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>KLF4</t>
+          <t>KLK6</t>
         </is>
       </c>
       <c r="B168" t="b">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G168" t="b">
@@ -5571,7 +5571,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>KLK6</t>
+          <t>KLRB1</t>
         </is>
       </c>
       <c r="B169" t="b">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G169" t="b">
@@ -5602,28 +5602,28 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>KLRB1</t>
+          <t>LAMA2</t>
         </is>
       </c>
       <c r="B170" t="b">
         <v>1</v>
       </c>
       <c r="C170">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Astro.2, Excit.L2_5.2, Oligo.4, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Vasc.VLMC, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5.2: 2.04, Oligo.4 specific Enrich genes t= 4.39, DEG carrier included: Astro.2 down</t>
         </is>
       </c>
       <c r="G170" t="b">
@@ -5633,28 +5633,28 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>LAMA2</t>
+          <t>LAMP5</t>
         </is>
       </c>
       <c r="B171" t="b">
         <v>1</v>
       </c>
       <c r="C171">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type specific</t>
+          <t>Base, Marker - SpD</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Astro.2, Excit.L2_5.2, Oligo.4, Vasc.VLMC</t>
+          <t>Inhib.Lamp5_Lhx6, L2.3~Sp09D01</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5.2: 2.04, Oligo.4 specific Enrich genes t= 4.39, DEG carrier included: Astro.2 down</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6, SpD MeanRatio gene: L2.3~Sp09D01/LD~Sp09D02: 2.406</t>
         </is>
       </c>
       <c r="G171" t="b">
@@ -5664,28 +5664,28 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>LAMP5</t>
+          <t>LERFS</t>
         </is>
       </c>
       <c r="B172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C172">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Base, Marker - SpD</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6, L2.3~Sp09D01</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6, SpD MeanRatio gene: L2.3~Sp09D01/LD~Sp09D02: 2.406</t>
+          <t>DEG carrier top: Oligo.3 down logFC=-1.39</t>
         </is>
       </c>
       <c r="G172" t="b">
@@ -5695,28 +5695,28 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>LERFS</t>
+          <t>LHX6</t>
         </is>
       </c>
       <c r="B173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 down logFC=-1.39</t>
+          <t>Base probe - Inhib.Chandelier</t>
         </is>
       </c>
       <c r="G173" t="b">
@@ -5726,28 +5726,28 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>LHX6</t>
+          <t>LINC00472</t>
         </is>
       </c>
       <c r="B174" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C174">
         <v>1</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Inhib.Chandelier</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier</t>
+          <t>DEG Ancestry op: Oligo.3 AA_down-EA_up*</t>
         </is>
       </c>
       <c r="G174" t="b">
@@ -5757,7 +5757,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>LINC00472</t>
+          <t>LINC00486</t>
         </is>
       </c>
       <c r="B175" t="b">
@@ -5768,17 +5768,17 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_down-EA_up*</t>
+          <t>DEG carrier top: Excit.L5.2 up</t>
         </is>
       </c>
       <c r="G175" t="b">
@@ -5788,7 +5788,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>LINC00486</t>
+          <t>LINC00609</t>
         </is>
       </c>
       <c r="B176" t="b">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Oligo.2</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L5.2 up</t>
+          <t>Oligo.2 specific Enrich genes t= 10.42</t>
         </is>
       </c>
       <c r="G176" t="b">
@@ -5819,7 +5819,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>LINC00609</t>
+          <t>LINC00706</t>
         </is>
       </c>
       <c r="B177" t="b">
@@ -5830,17 +5830,17 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Oligo.2</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Oligo.2 specific Enrich genes t= 10.42</t>
+          <t>DEG carrier top: Oligo.3 AA_down</t>
         </is>
       </c>
       <c r="G177" t="b">
@@ -5850,28 +5850,28 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>LINC00706</t>
+          <t>LINC01877</t>
         </is>
       </c>
       <c r="B178" t="b">
         <v>0</v>
       </c>
       <c r="C178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Marker - cell type global, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo.2</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 AA_down</t>
+          <t>globl MR genes -  Oligo.2/Oligo.1: 1.743, Oligo.2 specific MR genes - Oligo.2/Oligo.1: 1.743</t>
         </is>
       </c>
       <c r="G178" t="b">
@@ -5881,28 +5881,28 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>LINC01877</t>
+          <t>LINC02752</t>
         </is>
       </c>
       <c r="B179" t="b">
         <v>0</v>
       </c>
       <c r="C179">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Marker - cell type global, Marker - cell type specific</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Oligo.2</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>globl MR genes -  Oligo.2/Oligo.1: 1.743, Oligo.2 specific MR genes - Oligo.2/Oligo.1: 1.743</t>
+          <t>globl MR genes -  Excit.L5.2/Excit.L2_5.2: 10.797</t>
         </is>
       </c>
       <c r="G179" t="b">
@@ -5912,7 +5912,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>LINC02752</t>
+          <t>LINGO2</t>
         </is>
       </c>
       <c r="B180" t="b">
@@ -5923,17 +5923,17 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>globl MR genes -  Excit.L5.2/Excit.L2_5.2: 10.797</t>
+          <t>Oligo.3 specific Enrich genes t= 9.09</t>
         </is>
       </c>
       <c r="G180" t="b">
@@ -5943,7 +5943,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>LINGO2</t>
+          <t>LMO3</t>
         </is>
       </c>
       <c r="B181" t="b">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Oligo.3 specific Enrich genes t= 9.09</t>
+          <t>Astro.1 specific Enrich genes t= 8.73</t>
         </is>
       </c>
       <c r="G181" t="b">
@@ -5974,28 +5974,28 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>LMO3</t>
+          <t>LOX</t>
         </is>
       </c>
       <c r="B182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Astro.1 specific Enrich genes t= 8.73</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G182" t="b">
@@ -6005,28 +6005,28 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>LOX</t>
+          <t>LPAR1</t>
         </is>
       </c>
       <c r="B183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C183">
         <v>1</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Excit.L2_5.1</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>DEG carrier top: Excit.L2_5.1 down</t>
         </is>
       </c>
       <c r="G183" t="b">
@@ -6036,7 +6036,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>LPAR1</t>
+          <t>LRRC63</t>
         </is>
       </c>
       <c r="B184" t="b">
@@ -6047,17 +6047,17 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1</t>
+          <t>Oligo.2</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L2_5.1 down</t>
+          <t>globl MR genes -  Oligo.2/Oligo.1: 1.457</t>
         </is>
       </c>
       <c r="G184" t="b">
@@ -6787,21 +6787,21 @@
         <v>0</v>
       </c>
       <c r="C208">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>DEG - carrier, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L5.2, Oligo.3</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Oligo.3 specific MR genes - Oligo.3/Oligo.4: 1.141</t>
+          <t>Oligo.3 specific MR genes - Oligo.3/Oligo.4: 1.141, DEG carrier top: Excit.L5.2 down</t>
         </is>
       </c>
       <c r="G208" t="b">
@@ -6873,7 +6873,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>MT-ND4</t>
+          <t>MTX2</t>
         </is>
       </c>
       <c r="B211" t="b">
@@ -6884,17 +6884,17 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Oligo.2</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L5.2 down</t>
+          <t>Oligo.2 specific Enrich genes t= 11.38</t>
         </is>
       </c>
       <c r="G211" t="b">
@@ -6904,28 +6904,28 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>MTX2</t>
+          <t>MYO16</t>
         </is>
       </c>
       <c r="B212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C212">
         <v>1</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Oligo.2</t>
+          <t>Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Oligo.2 specific Enrich genes t= 11.38</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="G212" t="b">
@@ -6935,28 +6935,28 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MYO16</t>
+          <t>MYO5B</t>
         </is>
       </c>
       <c r="B213" t="b">
         <v>1</v>
       </c>
       <c r="C213">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6</t>
+          <t>Inhib.Pvalb</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6</t>
+          <t>Base probe - Inhib.Pvalb, globl MR genes -  Inhib.Pvalb/Inhib.Sst: 2.178</t>
         </is>
       </c>
       <c r="G213" t="b">
@@ -6966,28 +6966,28 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>MYO5B</t>
+          <t>MYRF</t>
         </is>
       </c>
       <c r="B214" t="b">
         <v>1</v>
       </c>
       <c r="C214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb, globl MR genes -  Inhib.Pvalb/Inhib.Sst: 2.178</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G214" t="b">
@@ -6997,28 +6997,28 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MYRF</t>
+          <t>NAP1L3</t>
         </is>
       </c>
       <c r="B215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C215">
         <v>1</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G215" t="b">
@@ -7028,28 +7028,28 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>NAP1L3</t>
+          <t>NCSTN</t>
         </is>
       </c>
       <c r="B216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C216">
         <v>1</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="G216" t="b">
@@ -7059,28 +7059,28 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>NCSTN</t>
+          <t>NDST4</t>
         </is>
       </c>
       <c r="B217" t="b">
         <v>1</v>
       </c>
       <c r="C217">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Excit.L5.2, Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Base probe - Inhib.Sst_Chold, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L5.1: 3.841</t>
         </is>
       </c>
       <c r="G217" t="b">
@@ -7090,28 +7090,28 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>NDST4</t>
+          <t>NES</t>
         </is>
       </c>
       <c r="B218" t="b">
         <v>1</v>
       </c>
       <c r="C218">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Excit.L5.2, Inhib.Sst_Chold</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L5.1: 3.841</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="G218" t="b">
@@ -7121,28 +7121,28 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>NES</t>
+          <t>NETO1</t>
         </is>
       </c>
       <c r="B219" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C219">
         <v>1</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>mediation gene: mediator Astro.2</t>
         </is>
       </c>
       <c r="G219" t="b">
@@ -7152,28 +7152,28 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>NETO1</t>
+          <t>NKG7</t>
         </is>
       </c>
       <c r="B220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C220">
         <v>1</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.2</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G220" t="b">
@@ -7183,28 +7183,28 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>NKG7</t>
+          <t>NLGN1</t>
         </is>
       </c>
       <c r="B221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C221">
         <v>1</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>DEG LR interactions: NLGN1 -&gt; NRXN1,NLGN1 -&gt; NRXN3,NRXN1 -&gt; NLGN1,NRXN3 -&gt; NLGN1</t>
         </is>
       </c>
       <c r="G221" t="b">
@@ -7214,28 +7214,28 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>NLGN1</t>
+          <t>NNAT</t>
         </is>
       </c>
       <c r="B222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C222">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>Base, Marker - cell type specific, Marker - SpD</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6b, Glioblastoma_cancer, L6~Sp09D04</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NLGN1 -&gt; NRXN1,NLGN1 -&gt; NRXN3,NRXN1 -&gt; NLGN1,NRXN3 -&gt; NLGN1</t>
+          <t>Base probe - Glioblastoma_cancer, Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 1.661, SpD MeanRatio gene: L6~Sp09D04/L2.3~Sp09D01: 1.542, SpD Enrich gene t=10.01</t>
         </is>
       </c>
       <c r="G222" t="b">
@@ -7245,28 +7245,28 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>NNAT</t>
+          <t>NOTCH1</t>
         </is>
       </c>
       <c r="B223" t="b">
         <v>1</v>
       </c>
       <c r="C223">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific, Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Excit.L6b, Glioblastoma_cancer, L6~Sp09D04</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 1.661, SpD MeanRatio gene: L6~Sp09D04/L2.3~Sp09D01: 1.542, SpD Enrich gene t=10.01</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="G223" t="b">
@@ -7276,28 +7276,28 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>NOTCH1</t>
+          <t>NPFFR2</t>
         </is>
       </c>
       <c r="B224" t="b">
         <v>1</v>
       </c>
       <c r="C224">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type global, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>Excit.L6_CT, Excit.L6b</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>Base probe - Excit.L6b, globl MR genes -  Excit.L6_CT/Excit.L2_5.1: 3.469, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2_5.1: 3.469</t>
         </is>
       </c>
       <c r="G224" t="b">
@@ -7307,7 +7307,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>NPFFR2</t>
+          <t>NPNT</t>
         </is>
       </c>
       <c r="B225" t="b">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Excit.L6_CT, Excit.L6b</t>
+          <t>Excit.L2_5.2, Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6b, globl MR genes -  Excit.L6_CT/Excit.L2_5.1: 3.469, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2_5.1: 3.469</t>
+          <t>Base probe - Inhib.Chandelier, globl MR genes -  Inhib.Chandelier/Excit.L2_5.2: 3.131, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5_6_NP: 6.062</t>
         </is>
       </c>
       <c r="G225" t="b">
@@ -7338,28 +7338,28 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>NPNT</t>
+          <t>NPTXR</t>
         </is>
       </c>
       <c r="B226" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C226">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global, Marker - cell type specific</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2, Inhib.Chandelier</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier, globl MR genes -  Inhib.Chandelier/Excit.L2_5.2: 3.131, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5_6_NP: 6.062</t>
+          <t>mediation gene: mediator Astro.1</t>
         </is>
       </c>
       <c r="G226" t="b">
@@ -7369,28 +7369,28 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>NPTXR</t>
+          <t>NPY1R</t>
         </is>
       </c>
       <c r="B227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C227">
         <v>1</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.1</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G227" t="b">
@@ -7400,7 +7400,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>NPY1R</t>
+          <t>NR2F2</t>
         </is>
       </c>
       <c r="B228" t="b">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="G228" t="b">
@@ -7431,28 +7431,28 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>NR2F2</t>
+          <t>NR4A2</t>
         </is>
       </c>
       <c r="B229" t="b">
         <v>1</v>
       </c>
       <c r="C229">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Glioblastoma_TME, Oligo.3</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Glioblastoma_TME, DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="G229" t="b">
@@ -7462,28 +7462,28 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>NR4A2</t>
+          <t>NRG3</t>
         </is>
       </c>
       <c r="B230" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME, Oligo.3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME, DEG carrier included: Oligo.3 up</t>
+          <t>DEG LR interactions: NRG3 -&gt; ERBB3</t>
         </is>
       </c>
       <c r="G230" t="b">
@@ -7493,28 +7493,28 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>NRG3</t>
+          <t>NRP1</t>
         </is>
       </c>
       <c r="B231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C231">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>Base, DEG - carrier, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6_CT, Macro, Vasc.Endo</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NRG3 -&gt; ERBB3</t>
+          <t>Base probe - Vasc.Endo, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2: 1.859, DEG carrier included: Macro down</t>
         </is>
       </c>
       <c r="G231" t="b">
@@ -7524,28 +7524,28 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>NRP1</t>
+          <t>NRXN1</t>
         </is>
       </c>
       <c r="B232" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C232">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type specific</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Excit.L6_CT, Macro, Vasc.Endo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2: 1.859, DEG carrier included: Macro down</t>
+          <t>DEG LR interactions: NLGN1 -&gt; NRXN1,NLGN4X -&gt; NRXN1,NRXN1 -&gt; NLGN1,NXPH1 -&gt; NRXN1</t>
         </is>
       </c>
       <c r="G232" t="b">
@@ -7555,7 +7555,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>NRXN1</t>
+          <t>NRXN3</t>
         </is>
       </c>
       <c r="B233" t="b">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NLGN1 -&gt; NRXN1,NLGN4X -&gt; NRXN1,NRXN1 -&gt; NLGN1,NXPH1 -&gt; NRXN1</t>
+          <t>DEG LR interactions: NLGN1 -&gt; NRXN3,NRXN3 -&gt; NLGN1,NXPH1 -&gt; NRXN3</t>
         </is>
       </c>
       <c r="G233" t="b">
@@ -7586,28 +7586,28 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>NRXN3</t>
+          <t>NTNG1</t>
         </is>
       </c>
       <c r="B234" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C234">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Astro.4, Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NLGN1 -&gt; NRXN3,NRXN3 -&gt; NLGN1,NXPH1 -&gt; NRXN3</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6, Astro.4 specific MR gene - Astro.4/Astro.2: 2.001</t>
         </is>
       </c>
       <c r="G234" t="b">
@@ -7617,28 +7617,28 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>NTNG1</t>
+          <t>NTNG2</t>
         </is>
       </c>
       <c r="B235" t="b">
         <v>1</v>
       </c>
       <c r="C235">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Astro.4, Inhib.Lamp5_Lhx6</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6, Astro.4 specific MR gene - Astro.4/Astro.2: 2.001</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G235" t="b">
@@ -7648,28 +7648,28 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>NTNG2</t>
+          <t>NTRK3</t>
         </is>
       </c>
       <c r="B236" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C236">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEGs - LR, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Oligo.3 specific Enrich genes t= 9.07, DEG LR interactions: NTRK3 -&gt; PTPRD</t>
         </is>
       </c>
       <c r="G236" t="b">
@@ -7679,28 +7679,28 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>NTRK3</t>
+          <t>NWD2</t>
         </is>
       </c>
       <c r="B237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>DEGs - LR, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Oligo.3 specific Enrich genes t= 9.07, DEG LR interactions: NTRK3 -&gt; PTPRD</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G237" t="b">
@@ -7710,28 +7710,28 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>NWD2</t>
+          <t>NXPH2</t>
         </is>
       </c>
       <c r="B238" t="b">
         <v>1</v>
       </c>
       <c r="C238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Excit.L5_6_NP, Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Inhib.Sst_Chold, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 16.109</t>
         </is>
       </c>
       <c r="G238" t="b">
@@ -7741,28 +7741,28 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>NXPH2</t>
+          <t>OLIG1</t>
         </is>
       </c>
       <c r="B239" t="b">
         <v>1</v>
       </c>
       <c r="C239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, Inhib.Sst_Chold</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 16.109</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="G239" t="b">
@@ -7772,28 +7772,28 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>OLIG1</t>
+          <t>OLIG2</t>
         </is>
       </c>
       <c r="B240" t="b">
         <v>1</v>
       </c>
       <c r="C240">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>OPC, OPC.4</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>Base probe - OPC, globl MR genes -  OPC.4/OPC.1: 1.089</t>
         </is>
       </c>
       <c r="G240" t="b">
@@ -7803,28 +7803,28 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>OLIG2</t>
+          <t>OPALIN</t>
         </is>
       </c>
       <c r="B241" t="b">
         <v>1</v>
       </c>
       <c r="C241">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Base, DEG - carrier, Marker - cell type global, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>OPC, OPC.4</t>
+          <t>Astro.3, Excit.L2_5.1, Oligo, Oligo.1, Oligo.3</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Base probe - OPC, globl MR genes -  OPC.4/OPC.1: 1.089</t>
+          <t>Base probe - Oligo, globl MR genes -  Oligo.1/Oligo.4: 1.2, Excit.L2_5.1 specific Enrich genes t= 7.46, Oligo.1 specific MR genes - Oligo.1/Oligo.4: 1.2, Oligo.1 specific Enrich genes t= 5.2, DEG carrier included: Astro.3 down, DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.65</t>
         </is>
       </c>
       <c r="G241" t="b">
@@ -7834,28 +7834,28 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>OPALIN</t>
+          <t>OST4</t>
         </is>
       </c>
       <c r="B242" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C242">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type global, Marker - cell type specific</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Astro.3, Excit.L2_5.1, Oligo, Oligo.1, Oligo.3</t>
+          <t>LD~Sp09D02</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, globl MR genes -  Oligo.1/Oligo.4: 1.2, Excit.L2_5.1 specific Enrich genes t= 7.46, Oligo.1 specific MR genes - Oligo.1/Oligo.4: 1.2, Oligo.1 specific Enrich genes t= 5.2, DEG carrier included: Astro.3 down, DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.65</t>
+          <t>SpD MeanRatio gene: LD~Sp09D02/L2.3~Sp09D01: 1.109</t>
         </is>
       </c>
       <c r="G242" t="b">
@@ -7865,28 +7865,28 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>OST4</t>
+          <t>OTOGL</t>
         </is>
       </c>
       <c r="B243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C243">
         <v>1</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>LD~Sp09D02</t>
+          <t>Excit.L4_IT</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>SpD MeanRatio gene: LD~Sp09D02/L2.3~Sp09D01: 1.109</t>
+          <t>Base probe - Excit.L4_IT</t>
         </is>
       </c>
       <c r="G243" t="b">
@@ -7896,28 +7896,28 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>OTOGL</t>
+          <t>P2RY12</t>
         </is>
       </c>
       <c r="B244" t="b">
         <v>1</v>
       </c>
       <c r="C244">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Excit.L4_IT</t>
+          <t>Macro, Micro</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT</t>
+          <t>Base probe - Micro, DEG carrier included: Macro down</t>
         </is>
       </c>
       <c r="G244" t="b">
@@ -7927,28 +7927,28 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>P2RY12</t>
+          <t>P2RY13</t>
         </is>
       </c>
       <c r="B245" t="b">
         <v>1</v>
       </c>
       <c r="C245">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Macro, Micro</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Base probe - Micro, DEG carrier included: Macro down</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G245" t="b">
@@ -7958,28 +7958,28 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>P2RY13</t>
+          <t>PABPN1</t>
         </is>
       </c>
       <c r="B246" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C246">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Astro.3, Excit.L2_5.1</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Astro.3 specific MR genes - Astro.3/Astro.1: 1.046, Excit.L2_5.1 specific Enrich genes t= 9.16</t>
         </is>
       </c>
       <c r="G246" t="b">
@@ -7989,28 +7989,28 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>PABPN1</t>
+          <t>PAX6</t>
         </is>
       </c>
       <c r="B247" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C247">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Astro.3, Excit.L2_5.1</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Astro.3 specific MR genes - Astro.3/Astro.1: 1.046, Excit.L2_5.1 specific Enrich genes t= 9.16</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="G247" t="b">
@@ -8020,28 +8020,28 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>PAX6</t>
+          <t>PCDH9-AS2</t>
         </is>
       </c>
       <c r="B248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C248">
         <v>1</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Astro.1 specific MR genes - Astro.1/Astro.3: 1.486</t>
         </is>
       </c>
       <c r="G248" t="b">
@@ -8051,28 +8051,28 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>PCDH9-AS2</t>
+          <t>PCNA</t>
         </is>
       </c>
       <c r="B249" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C249">
         <v>1</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Proliferation</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Astro.1 specific MR genes - Astro.1/Astro.3: 1.486</t>
+          <t>Base probe - Proliferation</t>
         </is>
       </c>
       <c r="G249" t="b">
@@ -8082,7 +8082,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PCNA</t>
+          <t>PCSK1</t>
         </is>
       </c>
       <c r="B250" t="b">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Proliferation</t>
+          <t>Excit.L5_ET</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Base probe - Proliferation</t>
+          <t>Base probe - Excit.L5_ET</t>
         </is>
       </c>
       <c r="G250" t="b">
@@ -8113,28 +8113,28 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>PCSK1</t>
+          <t>PCSK6</t>
         </is>
       </c>
       <c r="B251" t="b">
         <v>1</v>
       </c>
       <c r="C251">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, DEG - mediation</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Excit.L5_ET</t>
+          <t>Oligo, Oligo.3</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_ET</t>
+          <t>Base probe - Oligo, DEG carrier included: Oligo.3 down, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G251" t="b">
@@ -8144,28 +8144,28 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>PCSK6</t>
+          <t>PDGFD</t>
         </is>
       </c>
       <c r="B252" t="b">
         <v>1</v>
       </c>
       <c r="C252">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Oligo, Oligo.3</t>
+          <t>Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, DEG carrier included: Oligo.3 down, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6, globl MR genes -  Inhib.Lamp5_Lhx6/Excit.L2: 4.15</t>
         </is>
       </c>
       <c r="G252" t="b">
@@ -8175,28 +8175,28 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PDGFD</t>
+          <t>PDGFRA</t>
         </is>
       </c>
       <c r="B253" t="b">
         <v>1</v>
       </c>
       <c r="C253">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6, globl MR genes -  Inhib.Lamp5_Lhx6/Excit.L2: 4.15</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="G253" t="b">
@@ -8206,7 +8206,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PDGFRA</t>
+          <t>PECAM1</t>
         </is>
       </c>
       <c r="B254" t="b">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="G254" t="b">
@@ -8237,7 +8237,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>PECAM1</t>
+          <t>PHLDB2</t>
         </is>
       </c>
       <c r="B255" t="b">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="G255" t="b">
@@ -8268,28 +8268,28 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PHLDB2</t>
+          <t>PLCE1</t>
         </is>
       </c>
       <c r="B256" t="b">
         <v>1</v>
       </c>
       <c r="C256">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Astro.2, Astro.4, Excit.L6b, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Vasc.VLMC, Astro.4 specific MR gene - Astro.4/Astro.5: 3.668, Excit.L6b specific MR gene - Excit.L6b/Excit.L2_5.1: 4.023, DEG carrier included: Astro.2 down</t>
         </is>
       </c>
       <c r="G256" t="b">
@@ -8299,28 +8299,28 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PLCE1</t>
+          <t>PLCH1</t>
         </is>
       </c>
       <c r="B257" t="b">
         <v>1</v>
       </c>
       <c r="C257">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type specific</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Astro.2, Astro.4, Excit.L6b, Vasc.VLMC</t>
+          <t>Excit.L2_5.2, Inhib.Sst</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC, Astro.4 specific MR gene - Astro.4/Astro.5: 3.668, Excit.L6b specific MR gene - Excit.L6b/Excit.L2_5.1: 4.023, DEG carrier included: Astro.2 down</t>
+          <t>Base probe - Inhib.Sst, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5.1: 1.52</t>
         </is>
       </c>
       <c r="G257" t="b">
@@ -8330,28 +8330,28 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>PLCH1</t>
+          <t>PLD5</t>
         </is>
       </c>
       <c r="B258" t="b">
         <v>1</v>
       </c>
       <c r="C258">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2, Inhib.Sst</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5.1: 1.52</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="G258" t="b">
@@ -8361,28 +8361,28 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>PLD5</t>
+          <t>PLP1</t>
         </is>
       </c>
       <c r="B259" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C259">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Excit.L2_5.1, Oligo.3</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>Excit.L2_5.1 specific Enrich genes t= 8.05, DEG of interest: Oligo.3 down logFC=-0.93</t>
         </is>
       </c>
       <c r="G259" t="b">
@@ -8392,28 +8392,28 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PLP1</t>
+          <t>PLPPR4</t>
         </is>
       </c>
       <c r="B260" t="b">
         <v>0</v>
       </c>
       <c r="C260">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>DEG - carrier, Marker - cell type specific</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1, Oligo.3</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1 specific Enrich genes t= 8.05, DEG of interest: Oligo.3 down logFC=-0.93</t>
+          <t>mediation gene: mediator Astro.1</t>
         </is>
       </c>
       <c r="G260" t="b">
@@ -8423,28 +8423,28 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>PLPPR4</t>
+          <t>POSTN</t>
         </is>
       </c>
       <c r="B261" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.1</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G261" t="b">
@@ -8454,7 +8454,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>POSTN</t>
+          <t>POU6F2</t>
         </is>
       </c>
       <c r="B262" t="b">
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Excit.L4_IT</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Excit.L4_IT</t>
         </is>
       </c>
       <c r="G262" t="b">
@@ -8485,28 +8485,28 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>POU6F2</t>
+          <t>PROX1</t>
         </is>
       </c>
       <c r="B263" t="b">
         <v>1</v>
       </c>
       <c r="C263">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Excit.L4_IT</t>
+          <t>Inhib.Sncg, Inhib.Vip</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT</t>
+          <t>Base probe - Inhib.Sncg, globl MR genes -  Inhib.Vip/Oligo.2: 1.345</t>
         </is>
       </c>
       <c r="G263" t="b">
@@ -8516,28 +8516,28 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PROX1</t>
+          <t>PSEN1</t>
         </is>
       </c>
       <c r="B264" t="b">
         <v>1</v>
       </c>
       <c r="C264">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Base, DEG - carrier, Lit - AD risk</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Inhib.Sncg, Inhib.Vip</t>
+          <t>Oligo, Oligo.3</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sncg, globl MR genes -  Inhib.Vip/Oligo.2: 1.345</t>
+          <t>Base probe - Oligo, OpenTargets AD gene, DEG carrier included: Oligo.3 down</t>
         </is>
       </c>
       <c r="G264" t="b">
@@ -8547,28 +8547,28 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PSEN1</t>
+          <t>PSEN2</t>
         </is>
       </c>
       <c r="B265" t="b">
         <v>1</v>
       </c>
       <c r="C265">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Lit - AD risk</t>
+          <t>Base, Lit - AD risk</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Oligo, Oligo.3</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, OpenTargets AD gene, DEG carrier included: Oligo.3 down</t>
+          <t>Base probe - Glioblastoma_cancer, OpenTargets AD gene</t>
         </is>
       </c>
       <c r="G265" t="b">
@@ -8578,18 +8578,18 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PSEN2</t>
+          <t>PSENEN</t>
         </is>
       </c>
       <c r="B266" t="b">
         <v>1</v>
       </c>
       <c r="C266">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Base, Lit - AD risk</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, OpenTargets AD gene</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G266" t="b">
@@ -8609,7 +8609,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PSENEN</t>
+          <t>PTCHD4</t>
         </is>
       </c>
       <c r="B267" t="b">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Inhib.Lamp5</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Inhib.Lamp5</t>
         </is>
       </c>
       <c r="G267" t="b">
@@ -8640,28 +8640,28 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>PTCHD4</t>
+          <t>PTGDS</t>
         </is>
       </c>
       <c r="B268" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C268">
         <v>1</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5</t>
+          <t>Astro.2 specific MR genes - Astro.2/Astro.5: 1.01, Astro.2 specific Enrich genes t= 4.92</t>
         </is>
       </c>
       <c r="G268" t="b">
@@ -8671,28 +8671,28 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>PTGDS</t>
+          <t>PTPRC</t>
         </is>
       </c>
       <c r="B269" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C269">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, DEG - ancestry, DEG - carrier</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Micro, Oligo.3, Oligo.5</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Astro.2 specific MR genes - Astro.2/Astro.5: 1.01, Astro.2 specific Enrich genes t= 4.92</t>
+          <t>Base probe - Micro, DEG carrier included: Oligo.3 up, DEG carrier top: Oligo.3 up logFC=3.24, DEG carrier included: Oligo.5 up, DEG carrier top: Oligo.3 AA_up</t>
         </is>
       </c>
       <c r="G269" t="b">
@@ -8702,28 +8702,28 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>PTPRC</t>
+          <t>PTPRD</t>
         </is>
       </c>
       <c r="B270" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C270">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Base, DEG - ancestry, DEG - carrier</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Micro, Oligo.3, Oligo.5</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Base probe - Micro, DEG carrier included: Oligo.3 up, DEG carrier top: Oligo.3 up logFC=3.24, DEG carrier included: Oligo.5 up, DEG carrier top: Oligo.3 AA_up</t>
+          <t>DEG LR interactions: IL1RAPL1 -&gt; PTPRD,NTRK3 -&gt; PTPRD</t>
         </is>
       </c>
       <c r="G270" t="b">
@@ -8733,28 +8733,28 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PTPRD</t>
+          <t>PTPRZ1</t>
         </is>
       </c>
       <c r="B271" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C271">
         <v>1</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>DEG LR interactions: IL1RAPL1 -&gt; PTPRD,NTRK3 -&gt; PTPRD</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="G271" t="b">
@@ -8764,7 +8764,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>PTPRZ1</t>
+          <t>PVALB</t>
         </is>
       </c>
       <c r="B272" t="b">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>Base probe - Inhib.Chandelier</t>
         </is>
       </c>
       <c r="G272" t="b">
@@ -8795,28 +8795,28 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>PVALB</t>
+          <t>RABL2B</t>
         </is>
       </c>
       <c r="B273" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C273">
         <v>1</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Inhib.Chandelier</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
         </is>
       </c>
       <c r="G273" t="b">
@@ -8826,28 +8826,28 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>RABL2B</t>
+          <t>RASGRP1</t>
         </is>
       </c>
       <c r="B274" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G274" t="b">
@@ -8857,28 +8857,28 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>RASGRP1</t>
+          <t>RELN</t>
         </is>
       </c>
       <c r="B275" t="b">
         <v>1</v>
       </c>
       <c r="C275">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - SpD</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Inhib.Pax6, L2.3~Sp09D01</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Inhib.Pax6, SpD marker from Lit</t>
         </is>
       </c>
       <c r="G275" t="b">
@@ -8888,7 +8888,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>RELN</t>
+          <t>RFTN1</t>
         </is>
       </c>
       <c r="B276" t="b">
@@ -8899,17 +8899,17 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Base, Marker - SpD</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Inhib.Pax6, L2.3~Sp09D01</t>
+          <t>Oligo.3, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6, SpD marker from Lit</t>
+          <t>Base probe - Vasc.VLMC, DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="G276" t="b">
@@ -8919,28 +8919,28 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>RFTN1</t>
+          <t>RGS10</t>
         </is>
       </c>
       <c r="B277" t="b">
         <v>1</v>
       </c>
       <c r="C277">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Oligo.3, Vasc.VLMC</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC, DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G277" t="b">
@@ -8950,7 +8950,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>RGS10</t>
+          <t>RGS16</t>
         </is>
       </c>
       <c r="B278" t="b">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G278" t="b">
@@ -8981,28 +8981,28 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>RGS16</t>
+          <t>RIT2</t>
         </is>
       </c>
       <c r="B279" t="b">
         <v>1</v>
       </c>
       <c r="C279">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Excit.L2_5.2, Excit.L5_ET</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Excit.L5_ET, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L6_CT: 2.087</t>
         </is>
       </c>
       <c r="G279" t="b">
@@ -9012,28 +9012,28 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>RIT2</t>
+          <t>RNASE1</t>
         </is>
       </c>
       <c r="B280" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C280">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>MOFA - Factor3</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2, Excit.L5_ET</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_ET, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L6_CT: 2.087</t>
+          <t>MOFA Oligo.3 Factor3-</t>
         </is>
       </c>
       <c r="G280" t="b">
@@ -9043,28 +9043,28 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>RNASE1</t>
+          <t>RNASET2</t>
         </is>
       </c>
       <c r="B281" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C281">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>MOFA - Factor3</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME, Oligo.3</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>MOFA Oligo.3 Factor3-</t>
+          <t>Base probe - Glioblastoma_TME, DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="G281" t="b">
@@ -9074,28 +9074,28 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>RNASET2</t>
+          <t>RNF144B</t>
         </is>
       </c>
       <c r="B282" t="b">
         <v>1</v>
       </c>
       <c r="C282">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME, Oligo.3</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME, DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="G282" t="b">
@@ -9105,28 +9105,28 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>RNF144B</t>
+          <t>RORB</t>
         </is>
       </c>
       <c r="B283" t="b">
         <v>1</v>
       </c>
       <c r="C283">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>Excit.L4_IT, Excit.L5.1</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>Base probe - Excit.L4_IT, Excit.L5.1 specific MR gene - Excit.L5.1/Excit.L2_5.1: 4.221</t>
         </is>
       </c>
       <c r="G283" t="b">
@@ -9136,28 +9136,28 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>RORB</t>
+          <t>ROS1</t>
         </is>
       </c>
       <c r="B284" t="b">
         <v>1</v>
       </c>
       <c r="C284">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base, Marker - cell type global, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Excit.L4_IT, Excit.L5.1</t>
+          <t>Excit.L6b</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT, Excit.L5.1 specific MR gene - Excit.L5.1/Excit.L2_5.1: 4.221</t>
+          <t>Base probe - Excit.L6b, globl MR genes -  Excit.L6b/Excit.L2: 5.636, Excit.L6b specific MR gene - Excit.L6b/Excit.L2: 5.636</t>
         </is>
       </c>
       <c r="G284" t="b">
@@ -9167,28 +9167,28 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ROS1</t>
+          <t>RPS27</t>
         </is>
       </c>
       <c r="B285" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C285">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global, Marker - cell type specific</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Excit.L6b</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6b, globl MR genes -  Excit.L6b/Excit.L2: 5.636, Excit.L6b specific MR gene - Excit.L6b/Excit.L2: 5.636</t>
+          <t>Astro.3 specific MR genes - Astro.3/Astro.2: 1.109</t>
         </is>
       </c>
       <c r="G285" t="b">
@@ -9198,28 +9198,28 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>RPS27</t>
+          <t>RSPO2</t>
         </is>
       </c>
       <c r="B286" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C286">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Excit.L5.2, Inhib.Pvalb</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Astro.3 specific MR genes - Astro.3/Astro.2: 1.109</t>
+          <t>Base probe - Inhib.Pvalb, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2: 1.829</t>
         </is>
       </c>
       <c r="G286" t="b">
@@ -9229,28 +9229,28 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>RSPO2</t>
+          <t>RXFP1</t>
         </is>
       </c>
       <c r="B287" t="b">
         <v>1</v>
       </c>
       <c r="C287">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Excit.L5.2, Inhib.Pvalb</t>
+          <t>Excit.L5_IT</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2: 1.829</t>
+          <t>Base probe - Excit.L5_IT</t>
         </is>
       </c>
       <c r="G287" t="b">
@@ -9260,7 +9260,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>RXFP1</t>
+          <t>RYR3</t>
         </is>
       </c>
       <c r="B288" t="b">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Excit.L5_IT</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_IT</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="G288" t="b">
@@ -9291,7 +9291,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>RYR3</t>
+          <t>S100A4</t>
         </is>
       </c>
       <c r="B289" t="b">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G289" t="b">
@@ -9322,7 +9322,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>S100A4</t>
+          <t>SAMD5</t>
         </is>
       </c>
       <c r="B290" t="b">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Inhib.Pvalb</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Inhib.Pvalb</t>
         </is>
       </c>
       <c r="G290" t="b">
@@ -9353,28 +9353,28 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>SAMD5</t>
+          <t>SDK1</t>
         </is>
       </c>
       <c r="B291" t="b">
         <v>1</v>
       </c>
       <c r="C291">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb</t>
+          <t>Excit.L5_6_NP, Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb</t>
+          <t>Base probe - Inhib.Chandelier, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 1.88</t>
         </is>
       </c>
       <c r="G291" t="b">
@@ -9384,28 +9384,28 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>SDK1</t>
+          <t>SELENOP</t>
         </is>
       </c>
       <c r="B292" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C292">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>MOFA - Factor3</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, Inhib.Chandelier</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 1.88</t>
+          <t>MOFA Oligo.3 Factor3-</t>
         </is>
       </c>
       <c r="G292" t="b">
@@ -9415,28 +9415,28 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SELENOP</t>
+          <t>SEMA5A</t>
         </is>
       </c>
       <c r="B293" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C293">
         <v>1</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>MOFA - Factor3</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>MOFA Oligo.3 Factor3-</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="G293" t="b">
@@ -9446,28 +9446,28 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>SEMA5A</t>
+          <t>SEMA6D</t>
         </is>
       </c>
       <c r="B294" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C294">
         <v>1</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Oligo.1</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.2: 1.179</t>
         </is>
       </c>
       <c r="G294" t="b">
@@ -9477,28 +9477,28 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>SEMA6D</t>
+          <t>SERPINA3</t>
         </is>
       </c>
       <c r="B295" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Oligo.1</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.2: 1.179</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="G295" t="b">
@@ -9508,7 +9508,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>SERPINA3</t>
+          <t>SFRP2</t>
         </is>
       </c>
       <c r="B296" t="b">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="G296" t="b">
@@ -9539,28 +9539,28 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>SFRP2</t>
+          <t>SGSM3</t>
         </is>
       </c>
       <c r="B297" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C297">
         <v>1</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up*-EA_down</t>
         </is>
       </c>
       <c r="G297" t="b">
@@ -9570,28 +9570,28 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>SGSM3</t>
+          <t>SLC17A6</t>
         </is>
       </c>
       <c r="B298" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C298">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L4_IT, Excit.L5.2</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up*-EA_down</t>
+          <t>Base probe - Excit.L4_IT, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2: 1.542</t>
         </is>
       </c>
       <c r="G298" t="b">
@@ -9601,28 +9601,28 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>SLC17A6</t>
+          <t>SLC17A7</t>
         </is>
       </c>
       <c r="B299" t="b">
         <v>1</v>
       </c>
       <c r="C299">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base, DEG - carrier, DEG - mediation</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Excit.L4_IT, Excit.L5.2</t>
+          <t>Excit.L6b, Oligo.3</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2: 1.542</t>
+          <t>Base probe - Excit.L6b, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G299" t="b">
@@ -9632,28 +9632,28 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>SLC17A7</t>
+          <t>SLC24A2</t>
         </is>
       </c>
       <c r="B300" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C300">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Excit.L6b, Oligo.3</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6b, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Astro.3 specific Enrich genes t= 8.18</t>
         </is>
       </c>
       <c r="G300" t="b">
@@ -9663,28 +9663,28 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>SLC24A2</t>
+          <t>SLC24A3</t>
         </is>
       </c>
       <c r="B301" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C301">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, DEG - carrier, DEG - mediation</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Inhib.Vip, Oligo.3</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Astro.3 specific Enrich genes t= 8.18</t>
+          <t>Base probe - Inhib.Vip, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G301" t="b">
@@ -9694,28 +9694,28 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>SLC24A3</t>
+          <t>SLC26A4</t>
         </is>
       </c>
       <c r="B302" t="b">
         <v>1</v>
       </c>
       <c r="C302">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Inhib.Vip, Oligo.3</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Vip, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G302" t="b">
@@ -9725,28 +9725,28 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>SLC26A4</t>
+          <t>SLC4A4</t>
         </is>
       </c>
       <c r="B303" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C303">
         <v>1</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>MOFA - Factor3</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>MOFA Oligo.3 Factor3+</t>
         </is>
       </c>
       <c r="G303" t="b">
@@ -9756,28 +9756,28 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>SLC4A4</t>
+          <t>SLIT3</t>
         </is>
       </c>
       <c r="B304" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C304">
         <v>1</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>MOFA - Factor3</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L5_ET</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>MOFA Oligo.3 Factor3+</t>
+          <t>Base probe - Excit.L5_ET</t>
         </is>
       </c>
       <c r="G304" t="b">
@@ -9787,28 +9787,28 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>SLC5A11</t>
+          <t>SNCG</t>
         </is>
       </c>
       <c r="B305" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C305">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Oligo.2</t>
+          <t>Excit.L5_ET, Excit.L5.2</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>globl MR genes -  Oligo.2/Oligo.5: 1.492</t>
+          <t>Base probe - Excit.L5_ET, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.893</t>
         </is>
       </c>
       <c r="G305" t="b">
@@ -9818,28 +9818,28 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>SLIT3</t>
+          <t>SNRNP70</t>
         </is>
       </c>
       <c r="B306" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C306">
         <v>1</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Excit.L5_ET</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_ET</t>
+          <t>Astro.2 specific MR genes - Astro.2/Astro.3: 1.023</t>
         </is>
       </c>
       <c r="G306" t="b">
@@ -9849,28 +9849,28 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>SNCG</t>
+          <t>SNTA1</t>
         </is>
       </c>
       <c r="B307" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C307">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Excit.L5_ET, Excit.L5.2</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_ET, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.893</t>
+          <t>Astro.2 specific Enrich genes t= 4.98</t>
         </is>
       </c>
       <c r="G307" t="b">
@@ -9880,28 +9880,28 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>SNRNP70</t>
+          <t>SNTB2</t>
         </is>
       </c>
       <c r="B308" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C308">
         <v>1</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Excit.L6_IT</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Astro.2 specific MR genes - Astro.2/Astro.3: 1.023</t>
+          <t>Base probe - Excit.L6_IT</t>
         </is>
       </c>
       <c r="G308" t="b">
@@ -9911,7 +9911,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>SNTA1</t>
+          <t>SNX19</t>
         </is>
       </c>
       <c r="B309" t="b">
@@ -9922,17 +9922,17 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Astro.2 specific Enrich genes t= 4.98</t>
+          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
         </is>
       </c>
       <c r="G309" t="b">
@@ -9942,28 +9942,28 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SNTB2</t>
+          <t>SORBS1</t>
         </is>
       </c>
       <c r="B310" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C310">
         <v>1</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Excit.L6_IT</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G310" t="b">
@@ -9973,28 +9973,28 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>SNX19</t>
+          <t>SORCS1</t>
         </is>
       </c>
       <c r="B311" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C311">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base, DEG - carrier, DEG - mediation, Lit - AD risk</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L5_ET, Oligo.3</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
+          <t>Base probe - Excit.L5_ET, OpenTargets AD gene, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G311" t="b">
@@ -10004,28 +10004,28 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>SORBS1</t>
+          <t>SOX10</t>
         </is>
       </c>
       <c r="B312" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo.3, OPC</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>Base probe - OPC, DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.64</t>
         </is>
       </c>
       <c r="G312" t="b">
@@ -10035,28 +10035,28 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>SORCS1</t>
+          <t>SOX11</t>
         </is>
       </c>
       <c r="B313" t="b">
         <v>1</v>
       </c>
       <c r="C313">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, Lit - AD risk</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Excit.L5_ET, Oligo.3</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_ET, OpenTargets AD gene, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G313" t="b">
@@ -10066,28 +10066,28 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>SOX10</t>
+          <t>SOX2</t>
         </is>
       </c>
       <c r="B314" t="b">
         <v>1</v>
       </c>
       <c r="C314">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Oligo.3, OPC</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Base probe - OPC, DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.64</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G314" t="b">
@@ -10097,28 +10097,28 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>SOX11</t>
+          <t>SOX4</t>
         </is>
       </c>
       <c r="B315" t="b">
         <v>1</v>
       </c>
       <c r="C315">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Excit.L5_6_NP, Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Glioblastoma_cancer, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L5.2: 1.763</t>
         </is>
       </c>
       <c r="G315" t="b">
@@ -10128,7 +10128,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>SOX2</t>
+          <t>SOX9</t>
         </is>
       </c>
       <c r="B316" t="b">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="G316" t="b">
@@ -10159,28 +10159,28 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>SOX4</t>
+          <t>SPHKAP</t>
         </is>
       </c>
       <c r="B317" t="b">
         <v>1</v>
       </c>
       <c r="C317">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base, DEG - carrier, DEG - mediation</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, Glioblastoma_cancer</t>
+          <t>Inhib.Lamp5_Lhx6, Oligo.3</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L5.2: 1.763</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G317" t="b">
@@ -10190,7 +10190,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>SOX9</t>
+          <t>SPI1</t>
         </is>
       </c>
       <c r="B318" t="b">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G318" t="b">
@@ -10221,28 +10221,28 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>SPHKAP</t>
+          <t>SPON1</t>
         </is>
       </c>
       <c r="B319" t="b">
         <v>1</v>
       </c>
       <c r="C319">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6, Oligo.3</t>
+          <t>Astro, Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Astro, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.1: 3.554</t>
         </is>
       </c>
       <c r="G319" t="b">
@@ -10252,28 +10252,28 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>SPI1</t>
+          <t>SST</t>
         </is>
       </c>
       <c r="B320" t="b">
         <v>1</v>
       </c>
       <c r="C320">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Inhib.Sst, Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Inhib.Sst_Chold, globl MR genes -  Inhib.Sst/Inhib.Vip: 7.019</t>
         </is>
       </c>
       <c r="G320" t="b">
@@ -10283,28 +10283,28 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>SPON1</t>
+          <t>ST18</t>
         </is>
       </c>
       <c r="B321" t="b">
         <v>1</v>
       </c>
       <c r="C321">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Astro, Excit.L5_6_NP</t>
+          <t>Astro.2, Astro.3, Inhib.Vip, Oligo</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Base probe - Astro, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.1: 3.554</t>
+          <t>Base probe - Oligo, Astro.3 specific Enrich genes t= 7.88, DEG carrier included: Astro.2 down, DEG carrier included: Inhib.Vip down, mediation gene: mediator Astro.2</t>
         </is>
       </c>
       <c r="G321" t="b">
@@ -10314,28 +10314,28 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>SST</t>
+          <t>STAT1</t>
         </is>
       </c>
       <c r="B322" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C322">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Inhib.Sst, Inhib.Sst_Chold</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold, globl MR genes -  Inhib.Sst/Inhib.Vip: 7.019</t>
+          <t>DEG of interest: Oligo.3 up logFC=0.8</t>
         </is>
       </c>
       <c r="G322" t="b">
@@ -10345,28 +10345,28 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ST18</t>
+          <t>STAT3</t>
         </is>
       </c>
       <c r="B323" t="b">
         <v>1</v>
       </c>
       <c r="C323">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Astro.2, Astro.3, Inhib.Vip, Oligo</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, Astro.3 specific Enrich genes t= 7.88, DEG carrier included: Astro.2 down, DEG carrier included: Inhib.Vip down, mediation gene: mediator Astro.2</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="G323" t="b">
@@ -10376,7 +10376,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>STAT1</t>
+          <t>STAT4</t>
         </is>
       </c>
       <c r="B324" t="b">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>DEG of interest: Oligo.3 up logFC=0.8</t>
+          <t>DEG of interest: Oligo.3 up logFC=2.62</t>
         </is>
       </c>
       <c r="G324" t="b">
@@ -10407,7 +10407,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>STAT3</t>
+          <t>STK32B</t>
         </is>
       </c>
       <c r="B325" t="b">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="G325" t="b">
@@ -10438,28 +10438,28 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>STAT4</t>
+          <t>STXBP2</t>
         </is>
       </c>
       <c r="B326" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C326">
         <v>1</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>DEG of interest: Oligo.3 up logFC=2.62</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G326" t="b">
@@ -10469,28 +10469,28 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>STK32B</t>
+          <t>SULF1</t>
         </is>
       </c>
       <c r="B327" t="b">
         <v>1</v>
       </c>
       <c r="C327">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Excit.L6_CT, Inhib.Pvalb</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>Base probe - Inhib.Pvalb, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L6b: 4.385</t>
         </is>
       </c>
       <c r="G327" t="b">
@@ -10500,28 +10500,28 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>STXBP2</t>
+          <t>SV2B</t>
         </is>
       </c>
       <c r="B328" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C328">
         <v>1</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>mediation gene: mediator Astro.2</t>
         </is>
       </c>
       <c r="G328" t="b">
@@ -10531,28 +10531,28 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>SULF1</t>
+          <t>SYNPR</t>
         </is>
       </c>
       <c r="B329" t="b">
         <v>1</v>
       </c>
       <c r="C329">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Excit.L6_CT, Inhib.Pvalb</t>
+          <t>Inhib.Sst</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb, Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L6b: 4.385</t>
+          <t>Base probe - Inhib.Sst</t>
         </is>
       </c>
       <c r="G329" t="b">
@@ -10562,28 +10562,28 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>SV2B</t>
+          <t>TAC1</t>
         </is>
       </c>
       <c r="B330" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C330">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base, Marker - cell type global</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Inhib.Pvalb, Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.2</t>
+          <t>Base probe - Inhib.Sst_Chold, globl MR genes -  Inhib.Pvalb/Inhib.Sst: 2.127</t>
         </is>
       </c>
       <c r="G330" t="b">
@@ -10593,7 +10593,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>SYNPR</t>
+          <t>TACR1</t>
         </is>
       </c>
       <c r="B331" t="b">
@@ -10609,12 +10609,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Inhib.Sst</t>
+          <t>Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst</t>
+          <t>Base probe - Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="G331" t="b">
@@ -10624,28 +10624,28 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>TAC1</t>
+          <t>TANK</t>
         </is>
       </c>
       <c r="B332" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C332">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type global</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb, Inhib.Sst_Chold</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold, globl MR genes -  Inhib.Pvalb/Inhib.Sst: 2.127</t>
+          <t>Excit.L5.2 specific Enrich genes t= 13.71</t>
         </is>
       </c>
       <c r="G332" t="b">
@@ -10655,7 +10655,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>TACR1</t>
+          <t>TENM1</t>
         </is>
       </c>
       <c r="B333" t="b">
@@ -10671,12 +10671,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Inhib.Sst_Chold</t>
+          <t>Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold</t>
+          <t>Base probe - Inhib.Chandelier</t>
         </is>
       </c>
       <c r="G333" t="b">
@@ -10686,28 +10686,28 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>TANK</t>
+          <t>TESPA1</t>
         </is>
       </c>
       <c r="B334" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C334">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Excit.L2, Excit.L2_3_IT, Oligo.3</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Excit.L5.2 specific Enrich genes t= 13.71</t>
+          <t>Base probe - Excit.L2_3_IT, Excit.L2 specific MR gene - Excit.L2/Excit.L6b: 1.646, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G334" t="b">
@@ -10717,7 +10717,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>TENM1</t>
+          <t>TGFB1</t>
         </is>
       </c>
       <c r="B335" t="b">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Inhib.Chandelier</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G335" t="b">
@@ -10748,28 +10748,28 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>TESPA1</t>
+          <t>TGFB2</t>
         </is>
       </c>
       <c r="B336" t="b">
         <v>1</v>
       </c>
       <c r="C336">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Excit.L2, Excit.L2_3_IT, Oligo.3</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L2_3_IT, Excit.L2 specific MR gene - Excit.L2/Excit.L6b: 1.646, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="G336" t="b">
@@ -10779,28 +10779,28 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>TGFB1</t>
+          <t>TGFBI</t>
         </is>
       </c>
       <c r="B337" t="b">
         <v>1</v>
       </c>
       <c r="C337">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Excit.L2_5.2, Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Glioblastoma_TME, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L2_5.1: 12.753, Excit.L2_5.2 specific Enrich genes t= 11.97</t>
         </is>
       </c>
       <c r="G337" t="b">
@@ -10810,28 +10810,28 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>TGFB2</t>
+          <t>THBS1</t>
         </is>
       </c>
       <c r="B338" t="b">
         <v>1</v>
       </c>
       <c r="C338">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier, DEG - mediation</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Astro, Oligo.3</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Base probe - Astro, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="G338" t="b">
@@ -10841,28 +10841,28 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>TGFBI</t>
+          <t>THEMIS</t>
         </is>
       </c>
       <c r="B339" t="b">
         <v>1</v>
       </c>
       <c r="C339">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2, Glioblastoma_TME</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L2_5.1: 12.753, Excit.L2_5.2 specific Enrich genes t= 11.97</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G339" t="b">
@@ -10872,7 +10872,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>THBS1</t>
+          <t>THSD4</t>
         </is>
       </c>
       <c r="B340" t="b">
@@ -10883,17 +10883,17 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, DEG - mediation</t>
+          <t>Base, DEG - carrier, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Astro, Oligo.3</t>
+          <t>Excit.L2_5.2, Oligo.3, Vasc.Endo</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Base probe - Astro, DEG carrier included: Oligo.3 up, mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Vasc.Endo, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L2: 1.924, DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="G340" t="b">
@@ -10903,7 +10903,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>THEMIS</t>
+          <t>THSD7B</t>
         </is>
       </c>
       <c r="B341" t="b">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Inhib.Sncg</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Inhib.Sncg</t>
         </is>
       </c>
       <c r="G341" t="b">
@@ -10934,28 +10934,28 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>THSD4</t>
+          <t>TLR2</t>
         </is>
       </c>
       <c r="B342" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C342">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type specific</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2, Oligo.3, Vasc.Endo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo, Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L2: 1.924, DEG carrier included: Oligo.3 up</t>
+          <t>DEG of interest: Oligo.3 up logFC=1.56</t>
         </is>
       </c>
       <c r="G342" t="b">
@@ -10965,28 +10965,28 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>THSD7B</t>
+          <t>TMEM132C</t>
         </is>
       </c>
       <c r="B343" t="b">
         <v>1</v>
       </c>
       <c r="C343">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Inhib.Sncg</t>
+          <t>Excit.L5_6_NP, Vasc.VLMC</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sncg</t>
+          <t>Base probe - Vasc.VLMC, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.1: 5.943</t>
         </is>
       </c>
       <c r="G343" t="b">
@@ -10996,28 +10996,28 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>TLR2</t>
+          <t>TMIGD3</t>
         </is>
       </c>
       <c r="B344" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C344">
         <v>1</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>DEG of interest: Oligo.3 up logFC=1.56</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G344" t="b">
@@ -11027,28 +11027,28 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>TMEM132C</t>
+          <t>TNK2</t>
         </is>
       </c>
       <c r="B345" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C345">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, Vasc.VLMC</t>
+          <t>OPC.5</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.1: 5.943</t>
+          <t>OPC.5 specific MR genes - OPC.5/OPC.2: 1.04</t>
         </is>
       </c>
       <c r="G345" t="b">
@@ -11058,7 +11058,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>TMIGD3</t>
+          <t>TOP2A</t>
         </is>
       </c>
       <c r="B346" t="b">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Proliferation</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Proliferation</t>
         </is>
       </c>
       <c r="G346" t="b">
@@ -11089,28 +11089,28 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>TNK2</t>
+          <t>TP53</t>
         </is>
       </c>
       <c r="B347" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C347">
         <v>1</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>OPC.5</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>OPC.5 specific MR genes - OPC.5/OPC.2: 1.04</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="G347" t="b">
@@ -11120,7 +11120,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>TOP2A</t>
+          <t>TPH2</t>
         </is>
       </c>
       <c r="B348" t="b">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Proliferation</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Base probe - Proliferation</t>
+          <t>Base probe - Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="G348" t="b">
@@ -11151,7 +11151,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>TP53</t>
+          <t>TRAC</t>
         </is>
       </c>
       <c r="B349" t="b">
@@ -11167,12 +11167,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="G349" t="b">
@@ -11182,7 +11182,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>TPH2</t>
+          <t>TREM2</t>
         </is>
       </c>
       <c r="B350" t="b">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_6_NP</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="G350" t="b">
@@ -11213,28 +11213,28 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>TRAC</t>
+          <t>TRHDE</t>
         </is>
       </c>
       <c r="B351" t="b">
         <v>1</v>
       </c>
       <c r="C351">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Excit.L5_6_NP, Inhib.Sst</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Inhib.Sst, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.2: 1.521</t>
         </is>
       </c>
       <c r="G351" t="b">
@@ -11244,28 +11244,28 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>TREM2</t>
+          <t>TRIL</t>
         </is>
       </c>
       <c r="B352" t="b">
         <v>1</v>
       </c>
       <c r="C352">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Astro.2, Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Glioblastoma_cancer, DEG carrier included: Astro.2 up</t>
         </is>
       </c>
       <c r="G352" t="b">
@@ -11275,28 +11275,28 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>TRHDE</t>
+          <t>TRPC5</t>
         </is>
       </c>
       <c r="B353" t="b">
         <v>1</v>
       </c>
       <c r="C353">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP, Inhib.Sst</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.2: 1.521</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G353" t="b">
@@ -11306,28 +11306,28 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>TRIL</t>
+          <t>TRPC6</t>
         </is>
       </c>
       <c r="B354" t="b">
         <v>1</v>
       </c>
       <c r="C354">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Astro.2, Glioblastoma_cancer</t>
+          <t>Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, DEG carrier included: Astro.2 up</t>
+          <t>Base probe - Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="G354" t="b">
@@ -11337,28 +11337,28 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>TRIM51</t>
+          <t>TSHZ2</t>
         </is>
       </c>
       <c r="B355" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C355">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>WM.uf_Sp09D07-WM_Sp09D06</t>
+          <t>Astro.4, Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>SpD pw gene t=7.53</t>
+          <t>Base probe - Excit.L5_6_NP, Astro.4 specific MR gene - Astro.4/Astro.5: 4.669, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L5.1: 1.691</t>
         </is>
       </c>
       <c r="G355" t="b">
@@ -11368,28 +11368,28 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>TRPC5</t>
+          <t>TTYH1</t>
         </is>
       </c>
       <c r="B356" t="b">
         <v>1</v>
       </c>
       <c r="C356">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - SpD</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Glioblastoma_cancer, L1~Sp09D05</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Glioblastoma_cancer, SpD Enrich gene t=13.38</t>
         </is>
       </c>
       <c r="G356" t="b">
@@ -11399,28 +11399,28 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>TRPC6</t>
+          <t>UBXN2A</t>
         </is>
       </c>
       <c r="B357" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C357">
         <v>1</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Inhib.Sst_Chold</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold</t>
+          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
         </is>
       </c>
       <c r="G357" t="b">
@@ -11430,28 +11430,28 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>TSHZ2</t>
+          <t>UGT8</t>
         </is>
       </c>
       <c r="B358" t="b">
         <v>1</v>
       </c>
       <c r="C358">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base, DEG - carrier, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Astro.4, Excit.L5_6_NP</t>
+          <t>Astro.3, Oligo, Oligo.3</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_6_NP, Astro.4 specific MR gene - Astro.4/Astro.5: 4.669, Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L5.1: 1.691</t>
+          <t>Base probe - Oligo, Astro.3 specific Enrich genes t= 7.67, DEG carrier included: Astro.3 down, DEG carrier included: Oligo.3 down</t>
         </is>
       </c>
       <c r="G358" t="b">
@@ -11461,28 +11461,28 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>TTYH1</t>
+          <t>UNC5B</t>
         </is>
       </c>
       <c r="B359" t="b">
         <v>1</v>
       </c>
       <c r="C359">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Base, Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer, L1~Sp09D05</t>
+          <t>Inhib.Chandelier</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer, SpD Enrich gene t=13.38</t>
+          <t>Base probe - Inhib.Chandelier</t>
         </is>
       </c>
       <c r="G359" t="b">
@@ -11492,28 +11492,28 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>UBXN2A</t>
+          <t>VCAN</t>
         </is>
       </c>
       <c r="B360" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C360">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Astro.4, OPC</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
+          <t>Base probe - OPC, Astro.4 specific MR gene - Astro.4/Astro.5: 3.185</t>
         </is>
       </c>
       <c r="G360" t="b">
@@ -11523,28 +11523,28 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>UGT8</t>
+          <t>VIP</t>
         </is>
       </c>
       <c r="B361" t="b">
         <v>1</v>
       </c>
       <c r="C361">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Astro.3, Oligo, Oligo.3</t>
+          <t>Inhib.Vip</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Base probe - Oligo, Astro.3 specific Enrich genes t= 7.67, DEG carrier included: Astro.3 down, DEG carrier included: Oligo.3 down</t>
+          <t>Base probe - Inhib.Vip</t>
         </is>
       </c>
       <c r="G361" t="b">
@@ -11554,28 +11554,28 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>UNC5B</t>
+          <t>VPS54</t>
         </is>
       </c>
       <c r="B362" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C362">
         <v>1</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Inhib.Chandelier</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier</t>
+          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
         </is>
       </c>
       <c r="G362" t="b">
@@ -11585,7 +11585,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>VCAN</t>
+          <t>VWC2L</t>
         </is>
       </c>
       <c r="B363" t="b">
@@ -11596,17 +11596,17 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base, DEG - carrier</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Astro.4, OPC</t>
+          <t>Excit.L2_5.2, Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Base probe - OPC, Astro.4 specific MR gene - Astro.4/Astro.5: 3.185</t>
+          <t>Base probe - Excit.L5_6_NP, DEG carrier included: Excit.L2_5.2 up</t>
         </is>
       </c>
       <c r="G363" t="b">
@@ -11616,28 +11616,28 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>WIF1</t>
         </is>
       </c>
       <c r="B364" t="b">
         <v>1</v>
       </c>
       <c r="C364">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Base, Marker - cell type specific</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Inhib.Vip</t>
+          <t>Excit.L5.2, Inhib.Pax6</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Vip</t>
+          <t>Base probe - Inhib.Pax6, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.998</t>
         </is>
       </c>
       <c r="G364" t="b">
@@ -11647,28 +11647,28 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>VPS54</t>
+          <t>ZBBX</t>
         </is>
       </c>
       <c r="B365" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C365">
         <v>1</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L2_3_IT</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
+          <t>Base probe - Excit.L2_3_IT</t>
         </is>
       </c>
       <c r="G365" t="b">
@@ -11678,28 +11678,28 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>VWC2L</t>
+          <t>ZDHHC11</t>
         </is>
       </c>
       <c r="B366" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C366">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Base, DEG - carrier</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2, Excit.L5_6_NP</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_6_NP, DEG carrier included: Excit.L2_5.2 up</t>
+          <t>DEG carrier top: Excit.L5.2 down</t>
         </is>
       </c>
       <c r="G366" t="b">
@@ -11709,124 +11709,31 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>WIF1</t>
+          <t>ZDHHC23</t>
         </is>
       </c>
       <c r="B367" t="b">
         <v>1</v>
       </c>
       <c r="C367">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Base, Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Excit.L5.2, Inhib.Pax6</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6, Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.998</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="G367" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>ZBBX</t>
-        </is>
-      </c>
-      <c r="B368" t="b">
-        <v>1</v>
-      </c>
-      <c r="C368">
-        <v>1</v>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>Excit.L2_3_IT</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>Base probe - Excit.L2_3_IT</t>
-        </is>
-      </c>
-      <c r="G368" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>ZDHHC11</t>
-        </is>
-      </c>
-      <c r="B369" t="b">
-        <v>0</v>
-      </c>
-      <c r="C369">
-        <v>1</v>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>DEG - carrier</t>
-        </is>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>Excit.L5.2</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>DEG carrier top:  Excit.L5.2 down</t>
-        </is>
-      </c>
-      <c r="G369" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>ZDHHC23</t>
-        </is>
-      </c>
-      <c r="B370" t="b">
-        <v>1</v>
-      </c>
-      <c r="C370">
-        <v>1</v>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>Excit.L6_IT_Car3</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
-        </is>
-      </c>
-      <c r="G370" t="b">
         <v>1</v>
       </c>
     </row>
